--- a/NBA/step8_nba1q_direction_clean.xlsx
+++ b/NBA/step8_nba1q_direction_clean.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier D" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALL'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier A'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier B'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier C'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tier D'!$A$1:$BG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALL'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier A'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier B'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier C'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tier D'!$A$1:$BJ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG155"/>
+  <dimension ref="A1:BJ155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -838,30 +841,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -1067,12 +1085,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1278,12 +1303,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1489,12 +1521,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1680,12 +1719,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1887,12 +1933,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2098,12 +2151,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2293,12 +2353,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2492,12 +2559,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2683,12 +2757,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2890,12 +2971,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3097,12 +3185,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3288,12 +3383,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3487,12 +3589,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3686,12 +3795,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3893,12 +4009,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -4104,12 +4227,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -4311,12 +4441,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -4522,12 +4659,19 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -4733,12 +4877,19 @@
       <c r="BC20" s="3" t="inlineStr"/>
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr"/>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI20" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BJ20" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -4940,12 +5091,19 @@
       <c r="BC21" s="5" t="inlineStr"/>
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr">
+      <c r="BF21" s="5" t="inlineStr"/>
+      <c r="BG21" s="5" t="inlineStr"/>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG21" s="5" t="inlineStr">
+      <c r="BJ21" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -5147,12 +5305,19 @@
       <c r="BC22" s="3" t="inlineStr"/>
       <c r="BD22" s="3" t="inlineStr"/>
       <c r="BE22" s="3" t="inlineStr"/>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI22" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BJ22" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -5342,12 +5507,19 @@
       <c r="BC23" s="5" t="inlineStr"/>
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr"/>
-      <c r="BF23" s="5" t="inlineStr">
+      <c r="BF23" s="5" t="inlineStr"/>
+      <c r="BG23" s="5" t="inlineStr"/>
+      <c r="BH23" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI23" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG23" s="5" t="inlineStr">
+      <c r="BJ23" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -5553,12 +5725,19 @@
       <c r="BC24" s="3" t="inlineStr"/>
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI24" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BJ24" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -5744,12 +5923,19 @@
       <c r="BC25" s="5" t="inlineStr"/>
       <c r="BD25" s="5" t="inlineStr"/>
       <c r="BE25" s="5" t="inlineStr"/>
-      <c r="BF25" s="5" t="inlineStr">
+      <c r="BF25" s="5" t="inlineStr"/>
+      <c r="BG25" s="5" t="inlineStr"/>
+      <c r="BH25" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI25" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG25" s="5" t="inlineStr">
+      <c r="BJ25" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -5947,12 +6133,19 @@
       <c r="BC26" s="3" t="inlineStr"/>
       <c r="BD26" s="3" t="inlineStr"/>
       <c r="BE26" s="3" t="inlineStr"/>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="3" t="inlineStr"/>
+      <c r="BG26" s="3" t="inlineStr"/>
+      <c r="BH26" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI26" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BJ26" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6158,12 +6351,19 @@
       <c r="BC27" s="5" t="inlineStr"/>
       <c r="BD27" s="5" t="inlineStr"/>
       <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="5" t="inlineStr"/>
+      <c r="BG27" s="5" t="inlineStr"/>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BJ27" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -6365,12 +6565,19 @@
       <c r="BC28" s="3" t="inlineStr"/>
       <c r="BD28" s="3" t="inlineStr"/>
       <c r="BE28" s="3" t="inlineStr"/>
-      <c r="BF28" s="3" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI28" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG28" s="3" t="inlineStr">
+      <c r="BJ28" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -6576,12 +6783,19 @@
       <c r="BC29" s="5" t="inlineStr"/>
       <c r="BD29" s="5" t="inlineStr"/>
       <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr">
+      <c r="BF29" s="5" t="inlineStr"/>
+      <c r="BG29" s="5" t="inlineStr"/>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG29" s="5" t="inlineStr">
+      <c r="BJ29" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6767,12 +6981,19 @@
       <c r="BC30" s="3" t="inlineStr"/>
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr"/>
-      <c r="BF30" s="3" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI30" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG30" s="3" t="inlineStr">
+      <c r="BJ30" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -6966,12 +7187,19 @@
       <c r="BC31" s="5" t="inlineStr"/>
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr">
+      <c r="BF31" s="5" t="inlineStr"/>
+      <c r="BG31" s="5" t="inlineStr"/>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG31" s="5" t="inlineStr">
+      <c r="BJ31" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7145,12 +7373,19 @@
       <c r="BC32" s="3" t="inlineStr"/>
       <c r="BD32" s="3" t="inlineStr"/>
       <c r="BE32" s="3" t="inlineStr"/>
-      <c r="BF32" s="3" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI32" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG32" s="3" t="inlineStr">
+      <c r="BJ32" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -7352,12 +7587,19 @@
       <c r="BC33" s="5" t="inlineStr"/>
       <c r="BD33" s="5" t="inlineStr"/>
       <c r="BE33" s="5" t="inlineStr"/>
-      <c r="BF33" s="5" t="inlineStr">
+      <c r="BF33" s="5" t="inlineStr"/>
+      <c r="BG33" s="5" t="inlineStr"/>
+      <c r="BH33" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI33" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG33" s="5" t="inlineStr">
+      <c r="BJ33" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7559,12 +7801,19 @@
       <c r="BC34" s="3" t="inlineStr"/>
       <c r="BD34" s="3" t="inlineStr"/>
       <c r="BE34" s="3" t="inlineStr"/>
-      <c r="BF34" s="3" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr"/>
+      <c r="BG34" s="3" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI34" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG34" s="3" t="inlineStr">
+      <c r="BJ34" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7766,12 +8015,19 @@
       <c r="BC35" s="5" t="inlineStr"/>
       <c r="BD35" s="5" t="inlineStr"/>
       <c r="BE35" s="5" t="inlineStr"/>
-      <c r="BF35" s="5" t="inlineStr">
+      <c r="BF35" s="5" t="inlineStr"/>
+      <c r="BG35" s="5" t="inlineStr"/>
+      <c r="BH35" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI35" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG35" s="5" t="inlineStr">
+      <c r="BJ35" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7973,12 +8229,19 @@
       <c r="BC36" s="3" t="inlineStr"/>
       <c r="BD36" s="3" t="inlineStr"/>
       <c r="BE36" s="3" t="inlineStr"/>
-      <c r="BF36" s="3" t="inlineStr">
+      <c r="BF36" s="3" t="inlineStr"/>
+      <c r="BG36" s="3" t="inlineStr"/>
+      <c r="BH36" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI36" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG36" s="3" t="inlineStr">
+      <c r="BJ36" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -8184,12 +8447,19 @@
       <c r="BC37" s="5" t="inlineStr"/>
       <c r="BD37" s="5" t="inlineStr"/>
       <c r="BE37" s="5" t="inlineStr"/>
-      <c r="BF37" s="5" t="inlineStr">
+      <c r="BF37" s="5" t="inlineStr"/>
+      <c r="BG37" s="5" t="inlineStr"/>
+      <c r="BH37" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI37" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG37" s="5" t="inlineStr">
+      <c r="BJ37" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8395,12 +8665,19 @@
       <c r="BC38" s="3" t="inlineStr"/>
       <c r="BD38" s="3" t="inlineStr"/>
       <c r="BE38" s="3" t="inlineStr"/>
-      <c r="BF38" s="3" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr"/>
+      <c r="BG38" s="3" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI38" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG38" s="3" t="inlineStr">
+      <c r="BJ38" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8598,12 +8875,19 @@
       <c r="BC39" s="5" t="inlineStr"/>
       <c r="BD39" s="5" t="inlineStr"/>
       <c r="BE39" s="5" t="inlineStr"/>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="5" t="inlineStr"/>
+      <c r="BG39" s="5" t="inlineStr"/>
+      <c r="BH39" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI39" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr">
+      <c r="BJ39" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -8789,12 +9073,19 @@
       <c r="BC40" s="3" t="inlineStr"/>
       <c r="BD40" s="3" t="inlineStr"/>
       <c r="BE40" s="3" t="inlineStr"/>
-      <c r="BF40" s="3" t="inlineStr">
+      <c r="BF40" s="3" t="inlineStr"/>
+      <c r="BG40" s="3" t="inlineStr"/>
+      <c r="BH40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI40" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG40" s="3" t="inlineStr">
+      <c r="BJ40" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8988,12 +9279,19 @@
       <c r="BC41" s="5" t="inlineStr"/>
       <c r="BD41" s="5" t="inlineStr"/>
       <c r="BE41" s="5" t="inlineStr"/>
-      <c r="BF41" s="5" t="inlineStr">
+      <c r="BF41" s="5" t="inlineStr"/>
+      <c r="BG41" s="5" t="inlineStr"/>
+      <c r="BH41" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI41" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG41" s="5" t="inlineStr">
+      <c r="BJ41" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9199,12 +9497,19 @@
       <c r="BC42" s="3" t="inlineStr"/>
       <c r="BD42" s="3" t="inlineStr"/>
       <c r="BE42" s="3" t="inlineStr"/>
-      <c r="BF42" s="3" t="inlineStr">
+      <c r="BF42" s="3" t="inlineStr"/>
+      <c r="BG42" s="3" t="inlineStr"/>
+      <c r="BH42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI42" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG42" s="3" t="inlineStr">
+      <c r="BJ42" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -9398,12 +9703,19 @@
       <c r="BC43" s="5" t="inlineStr"/>
       <c r="BD43" s="5" t="inlineStr"/>
       <c r="BE43" s="5" t="inlineStr"/>
-      <c r="BF43" s="5" t="inlineStr">
+      <c r="BF43" s="5" t="inlineStr"/>
+      <c r="BG43" s="5" t="inlineStr"/>
+      <c r="BH43" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI43" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG43" s="5" t="inlineStr">
+      <c r="BJ43" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9597,12 +9909,19 @@
       <c r="BC44" s="3" t="inlineStr"/>
       <c r="BD44" s="3" t="inlineStr"/>
       <c r="BE44" s="3" t="inlineStr"/>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="3" t="inlineStr"/>
+      <c r="BG44" s="3" t="inlineStr"/>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI44" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BJ44" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9796,12 +10115,19 @@
       <c r="BC45" s="5" t="inlineStr"/>
       <c r="BD45" s="5" t="inlineStr"/>
       <c r="BE45" s="5" t="inlineStr"/>
-      <c r="BF45" s="5" t="inlineStr">
+      <c r="BF45" s="5" t="inlineStr"/>
+      <c r="BG45" s="5" t="inlineStr"/>
+      <c r="BH45" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI45" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG45" s="5" t="inlineStr">
+      <c r="BJ45" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9987,12 +10313,19 @@
       <c r="BC46" s="3" t="inlineStr"/>
       <c r="BD46" s="3" t="inlineStr"/>
       <c r="BE46" s="3" t="inlineStr"/>
-      <c r="BF46" s="3" t="inlineStr">
+      <c r="BF46" s="3" t="inlineStr"/>
+      <c r="BG46" s="3" t="inlineStr"/>
+      <c r="BH46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI46" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG46" s="3" t="inlineStr">
+      <c r="BJ46" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10198,12 +10531,19 @@
       <c r="BC47" s="5" t="inlineStr"/>
       <c r="BD47" s="5" t="inlineStr"/>
       <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr">
+      <c r="BF47" s="5" t="inlineStr"/>
+      <c r="BG47" s="5" t="inlineStr"/>
+      <c r="BH47" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI47" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG47" s="5" t="inlineStr">
+      <c r="BJ47" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10385,12 +10725,19 @@
       <c r="BC48" s="3" t="inlineStr"/>
       <c r="BD48" s="3" t="inlineStr"/>
       <c r="BE48" s="3" t="inlineStr"/>
-      <c r="BF48" s="3" t="inlineStr">
+      <c r="BF48" s="3" t="inlineStr"/>
+      <c r="BG48" s="3" t="inlineStr"/>
+      <c r="BH48" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI48" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BJ48" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10568,12 +10915,19 @@
       <c r="BC49" s="5" t="inlineStr"/>
       <c r="BD49" s="5" t="inlineStr"/>
       <c r="BE49" s="5" t="inlineStr"/>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="5" t="inlineStr"/>
+      <c r="BG49" s="5" t="inlineStr"/>
+      <c r="BH49" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI49" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BJ49" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10779,12 +11133,19 @@
       <c r="BC50" s="3" t="inlineStr"/>
       <c r="BD50" s="3" t="inlineStr"/>
       <c r="BE50" s="3" t="inlineStr"/>
-      <c r="BF50" s="3" t="inlineStr">
+      <c r="BF50" s="3" t="inlineStr"/>
+      <c r="BG50" s="3" t="inlineStr"/>
+      <c r="BH50" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI50" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG50" s="3" t="inlineStr">
+      <c r="BJ50" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10986,12 +11347,19 @@
       <c r="BC51" s="5" t="inlineStr"/>
       <c r="BD51" s="5" t="inlineStr"/>
       <c r="BE51" s="5" t="inlineStr"/>
-      <c r="BF51" s="5" t="inlineStr">
+      <c r="BF51" s="5" t="inlineStr"/>
+      <c r="BG51" s="5" t="inlineStr"/>
+      <c r="BH51" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI51" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG51" s="5" t="inlineStr">
+      <c r="BJ51" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11189,12 +11557,19 @@
       <c r="BC52" s="3" t="inlineStr"/>
       <c r="BD52" s="3" t="inlineStr"/>
       <c r="BE52" s="3" t="inlineStr"/>
-      <c r="BF52" s="3" t="inlineStr">
+      <c r="BF52" s="3" t="inlineStr"/>
+      <c r="BG52" s="3" t="inlineStr"/>
+      <c r="BH52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI52" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG52" s="3" t="inlineStr">
+      <c r="BJ52" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -11400,12 +11775,19 @@
       <c r="BC53" s="5" t="inlineStr"/>
       <c r="BD53" s="5" t="inlineStr"/>
       <c r="BE53" s="5" t="inlineStr"/>
-      <c r="BF53" s="5" t="inlineStr">
+      <c r="BF53" s="5" t="inlineStr"/>
+      <c r="BG53" s="5" t="inlineStr"/>
+      <c r="BH53" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI53" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG53" s="5" t="inlineStr">
+      <c r="BJ53" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11595,12 +11977,19 @@
       <c r="BC54" s="3" t="inlineStr"/>
       <c r="BD54" s="3" t="inlineStr"/>
       <c r="BE54" s="3" t="inlineStr"/>
-      <c r="BF54" s="3" t="inlineStr">
+      <c r="BF54" s="3" t="inlineStr"/>
+      <c r="BG54" s="3" t="inlineStr"/>
+      <c r="BH54" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI54" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG54" s="3" t="inlineStr">
+      <c r="BJ54" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11806,12 +12195,19 @@
       <c r="BC55" s="5" t="inlineStr"/>
       <c r="BD55" s="5" t="inlineStr"/>
       <c r="BE55" s="5" t="inlineStr"/>
-      <c r="BF55" s="5" t="inlineStr">
+      <c r="BF55" s="5" t="inlineStr"/>
+      <c r="BG55" s="5" t="inlineStr"/>
+      <c r="BH55" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI55" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG55" s="5" t="inlineStr">
+      <c r="BJ55" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -11993,12 +12389,19 @@
       <c r="BC56" s="3" t="inlineStr"/>
       <c r="BD56" s="3" t="inlineStr"/>
       <c r="BE56" s="3" t="inlineStr"/>
-      <c r="BF56" s="3" t="inlineStr">
+      <c r="BF56" s="3" t="inlineStr"/>
+      <c r="BG56" s="3" t="inlineStr"/>
+      <c r="BH56" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI56" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG56" s="3" t="inlineStr">
+      <c r="BJ56" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -12200,12 +12603,19 @@
       <c r="BC57" s="5" t="inlineStr"/>
       <c r="BD57" s="5" t="inlineStr"/>
       <c r="BE57" s="5" t="inlineStr"/>
-      <c r="BF57" s="5" t="inlineStr">
+      <c r="BF57" s="5" t="inlineStr"/>
+      <c r="BG57" s="5" t="inlineStr"/>
+      <c r="BH57" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI57" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG57" s="5" t="inlineStr">
+      <c r="BJ57" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12403,12 +12813,19 @@
       <c r="BC58" s="3" t="inlineStr"/>
       <c r="BD58" s="3" t="inlineStr"/>
       <c r="BE58" s="3" t="inlineStr"/>
-      <c r="BF58" s="3" t="inlineStr">
+      <c r="BF58" s="3" t="inlineStr"/>
+      <c r="BG58" s="3" t="inlineStr"/>
+      <c r="BH58" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI58" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BJ58" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12614,12 +13031,19 @@
       <c r="BC59" s="5" t="inlineStr"/>
       <c r="BD59" s="5" t="inlineStr"/>
       <c r="BE59" s="5" t="inlineStr"/>
-      <c r="BF59" s="5" t="inlineStr">
+      <c r="BF59" s="5" t="inlineStr"/>
+      <c r="BG59" s="5" t="inlineStr"/>
+      <c r="BH59" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI59" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG59" s="5" t="inlineStr">
+      <c r="BJ59" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12809,12 +13233,19 @@
       <c r="BC60" s="3" t="inlineStr"/>
       <c r="BD60" s="3" t="inlineStr"/>
       <c r="BE60" s="3" t="inlineStr"/>
-      <c r="BF60" s="3" t="inlineStr">
+      <c r="BF60" s="3" t="inlineStr"/>
+      <c r="BG60" s="3" t="inlineStr"/>
+      <c r="BH60" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI60" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG60" s="3" t="inlineStr">
+      <c r="BJ60" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13024,12 +13455,19 @@
       <c r="BC61" s="5" t="inlineStr"/>
       <c r="BD61" s="5" t="inlineStr"/>
       <c r="BE61" s="5" t="inlineStr"/>
-      <c r="BF61" s="5" t="inlineStr">
+      <c r="BF61" s="5" t="inlineStr"/>
+      <c r="BG61" s="5" t="inlineStr"/>
+      <c r="BH61" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI61" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG61" s="5" t="inlineStr">
+      <c r="BJ61" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13239,12 +13677,19 @@
       <c r="BC62" s="3" t="inlineStr"/>
       <c r="BD62" s="3" t="inlineStr"/>
       <c r="BE62" s="3" t="inlineStr"/>
-      <c r="BF62" s="3" t="inlineStr">
+      <c r="BF62" s="3" t="inlineStr"/>
+      <c r="BG62" s="3" t="inlineStr"/>
+      <c r="BH62" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI62" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG62" s="3" t="inlineStr">
+      <c r="BJ62" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13454,12 +13899,19 @@
       <c r="BC63" s="5" t="inlineStr"/>
       <c r="BD63" s="5" t="inlineStr"/>
       <c r="BE63" s="5" t="inlineStr"/>
-      <c r="BF63" s="5" t="inlineStr">
+      <c r="BF63" s="5" t="inlineStr"/>
+      <c r="BG63" s="5" t="inlineStr"/>
+      <c r="BH63" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI63" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG63" s="5" t="inlineStr">
+      <c r="BJ63" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13669,12 +14121,19 @@
       <c r="BC64" s="3" t="inlineStr"/>
       <c r="BD64" s="3" t="inlineStr"/>
       <c r="BE64" s="3" t="inlineStr"/>
-      <c r="BF64" s="3" t="inlineStr">
+      <c r="BF64" s="3" t="inlineStr"/>
+      <c r="BG64" s="3" t="inlineStr"/>
+      <c r="BH64" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI64" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG64" s="3" t="inlineStr">
+      <c r="BJ64" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13884,12 +14343,19 @@
       <c r="BC65" s="5" t="inlineStr"/>
       <c r="BD65" s="5" t="inlineStr"/>
       <c r="BE65" s="5" t="inlineStr"/>
-      <c r="BF65" s="5" t="inlineStr">
+      <c r="BF65" s="5" t="inlineStr"/>
+      <c r="BG65" s="5" t="inlineStr"/>
+      <c r="BH65" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI65" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG65" s="5" t="inlineStr">
+      <c r="BJ65" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14099,12 +14565,19 @@
       <c r="BC66" s="3" t="inlineStr"/>
       <c r="BD66" s="3" t="inlineStr"/>
       <c r="BE66" s="3" t="inlineStr"/>
-      <c r="BF66" s="3" t="inlineStr">
+      <c r="BF66" s="3" t="inlineStr"/>
+      <c r="BG66" s="3" t="inlineStr"/>
+      <c r="BH66" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI66" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG66" s="3" t="inlineStr">
+      <c r="BJ66" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14302,12 +14775,19 @@
       <c r="BC67" s="5" t="inlineStr"/>
       <c r="BD67" s="5" t="inlineStr"/>
       <c r="BE67" s="5" t="inlineStr"/>
-      <c r="BF67" s="5" t="inlineStr">
+      <c r="BF67" s="5" t="inlineStr"/>
+      <c r="BG67" s="5" t="inlineStr"/>
+      <c r="BH67" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI67" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG67" s="5" t="inlineStr">
+      <c r="BJ67" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14517,12 +14997,19 @@
       <c r="BC68" s="3" t="inlineStr"/>
       <c r="BD68" s="3" t="inlineStr"/>
       <c r="BE68" s="3" t="inlineStr"/>
-      <c r="BF68" s="3" t="inlineStr">
+      <c r="BF68" s="3" t="inlineStr"/>
+      <c r="BG68" s="3" t="inlineStr"/>
+      <c r="BH68" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI68" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG68" s="3" t="inlineStr">
+      <c r="BJ68" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -14716,12 +15203,19 @@
       <c r="BC69" s="5" t="inlineStr"/>
       <c r="BD69" s="5" t="inlineStr"/>
       <c r="BE69" s="5" t="inlineStr"/>
-      <c r="BF69" s="5" t="inlineStr">
+      <c r="BF69" s="5" t="inlineStr"/>
+      <c r="BG69" s="5" t="inlineStr"/>
+      <c r="BH69" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI69" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG69" s="5" t="inlineStr">
+      <c r="BJ69" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14907,12 +15401,19 @@
       <c r="BC70" s="3" t="inlineStr"/>
       <c r="BD70" s="3" t="inlineStr"/>
       <c r="BE70" s="3" t="inlineStr"/>
-      <c r="BF70" s="3" t="inlineStr">
+      <c r="BF70" s="3" t="inlineStr"/>
+      <c r="BG70" s="3" t="inlineStr"/>
+      <c r="BH70" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI70" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG70" s="3" t="inlineStr">
+      <c r="BJ70" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -15122,12 +15623,19 @@
       <c r="BC71" s="5" t="inlineStr"/>
       <c r="BD71" s="5" t="inlineStr"/>
       <c r="BE71" s="5" t="inlineStr"/>
-      <c r="BF71" s="5" t="inlineStr">
+      <c r="BF71" s="5" t="inlineStr"/>
+      <c r="BG71" s="5" t="inlineStr"/>
+      <c r="BH71" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI71" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG71" s="5" t="inlineStr">
+      <c r="BJ71" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -15313,12 +15821,19 @@
       <c r="BC72" s="3" t="inlineStr"/>
       <c r="BD72" s="3" t="inlineStr"/>
       <c r="BE72" s="3" t="inlineStr"/>
-      <c r="BF72" s="3" t="inlineStr">
+      <c r="BF72" s="3" t="inlineStr"/>
+      <c r="BG72" s="3" t="inlineStr"/>
+      <c r="BH72" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI72" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG72" s="3" t="inlineStr">
+      <c r="BJ72" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -15528,12 +16043,19 @@
       <c r="BC73" s="5" t="inlineStr"/>
       <c r="BD73" s="5" t="inlineStr"/>
       <c r="BE73" s="5" t="inlineStr"/>
-      <c r="BF73" s="5" t="inlineStr">
+      <c r="BF73" s="5" t="inlineStr"/>
+      <c r="BG73" s="5" t="inlineStr"/>
+      <c r="BH73" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI73" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG73" s="5" t="inlineStr">
+      <c r="BJ73" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -15719,12 +16241,19 @@
       <c r="BC74" s="3" t="inlineStr"/>
       <c r="BD74" s="3" t="inlineStr"/>
       <c r="BE74" s="3" t="inlineStr"/>
-      <c r="BF74" s="3" t="inlineStr">
+      <c r="BF74" s="3" t="inlineStr"/>
+      <c r="BG74" s="3" t="inlineStr"/>
+      <c r="BH74" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI74" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG74" s="3" t="inlineStr">
+      <c r="BJ74" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -15934,12 +16463,19 @@
       <c r="BC75" s="5" t="inlineStr"/>
       <c r="BD75" s="5" t="inlineStr"/>
       <c r="BE75" s="5" t="inlineStr"/>
-      <c r="BF75" s="5" t="inlineStr">
+      <c r="BF75" s="5" t="inlineStr"/>
+      <c r="BG75" s="5" t="inlineStr"/>
+      <c r="BH75" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI75" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG75" s="5" t="inlineStr">
+      <c r="BJ75" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -16149,12 +16685,19 @@
       <c r="BC76" s="3" t="inlineStr"/>
       <c r="BD76" s="3" t="inlineStr"/>
       <c r="BE76" s="3" t="inlineStr"/>
-      <c r="BF76" s="3" t="inlineStr">
+      <c r="BF76" s="3" t="inlineStr"/>
+      <c r="BG76" s="3" t="inlineStr"/>
+      <c r="BH76" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI76" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG76" s="3" t="inlineStr">
+      <c r="BJ76" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -16336,12 +16879,19 @@
       <c r="BC77" s="5" t="inlineStr"/>
       <c r="BD77" s="5" t="inlineStr"/>
       <c r="BE77" s="5" t="inlineStr"/>
-      <c r="BF77" s="5" t="inlineStr">
+      <c r="BF77" s="5" t="inlineStr"/>
+      <c r="BG77" s="5" t="inlineStr"/>
+      <c r="BH77" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI77" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG77" s="5" t="inlineStr">
+      <c r="BJ77" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -16547,12 +17097,19 @@
       <c r="BC78" s="3" t="inlineStr"/>
       <c r="BD78" s="3" t="inlineStr"/>
       <c r="BE78" s="3" t="inlineStr"/>
-      <c r="BF78" s="3" t="inlineStr">
+      <c r="BF78" s="3" t="inlineStr"/>
+      <c r="BG78" s="3" t="inlineStr"/>
+      <c r="BH78" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI78" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG78" s="3" t="inlineStr">
+      <c r="BJ78" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -16746,12 +17303,19 @@
       <c r="BC79" s="5" t="inlineStr"/>
       <c r="BD79" s="5" t="inlineStr"/>
       <c r="BE79" s="5" t="inlineStr"/>
-      <c r="BF79" s="5" t="inlineStr">
+      <c r="BF79" s="5" t="inlineStr"/>
+      <c r="BG79" s="5" t="inlineStr"/>
+      <c r="BH79" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI79" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG79" s="5" t="inlineStr">
+      <c r="BJ79" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -16961,12 +17525,19 @@
       <c r="BC80" s="3" t="inlineStr"/>
       <c r="BD80" s="3" t="inlineStr"/>
       <c r="BE80" s="3" t="inlineStr"/>
-      <c r="BF80" s="3" t="inlineStr">
+      <c r="BF80" s="3" t="inlineStr"/>
+      <c r="BG80" s="3" t="inlineStr"/>
+      <c r="BH80" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI80" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG80" s="3" t="inlineStr">
+      <c r="BJ80" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17160,12 +17731,19 @@
       <c r="BC81" s="5" t="inlineStr"/>
       <c r="BD81" s="5" t="inlineStr"/>
       <c r="BE81" s="5" t="inlineStr"/>
-      <c r="BF81" s="5" t="inlineStr">
+      <c r="BF81" s="5" t="inlineStr"/>
+      <c r="BG81" s="5" t="inlineStr"/>
+      <c r="BH81" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI81" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG81" s="5" t="inlineStr">
+      <c r="BJ81" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -17355,12 +17933,19 @@
       <c r="BC82" s="3" t="inlineStr"/>
       <c r="BD82" s="3" t="inlineStr"/>
       <c r="BE82" s="3" t="inlineStr"/>
-      <c r="BF82" s="3" t="inlineStr">
+      <c r="BF82" s="3" t="inlineStr"/>
+      <c r="BG82" s="3" t="inlineStr"/>
+      <c r="BH82" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI82" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG82" s="3" t="inlineStr">
+      <c r="BJ82" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17566,12 +18151,19 @@
       <c r="BC83" s="5" t="inlineStr"/>
       <c r="BD83" s="5" t="inlineStr"/>
       <c r="BE83" s="5" t="inlineStr"/>
-      <c r="BF83" s="5" t="inlineStr">
+      <c r="BF83" s="5" t="inlineStr"/>
+      <c r="BG83" s="5" t="inlineStr"/>
+      <c r="BH83" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI83" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG83" s="5" t="inlineStr">
+      <c r="BJ83" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -17749,12 +18341,19 @@
       <c r="BC84" s="3" t="inlineStr"/>
       <c r="BD84" s="3" t="inlineStr"/>
       <c r="BE84" s="3" t="inlineStr"/>
-      <c r="BF84" s="3" t="inlineStr">
+      <c r="BF84" s="3" t="inlineStr"/>
+      <c r="BG84" s="3" t="inlineStr"/>
+      <c r="BH84" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI84" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG84" s="3" t="inlineStr">
+      <c r="BJ84" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17964,12 +18563,19 @@
       <c r="BC85" s="5" t="inlineStr"/>
       <c r="BD85" s="5" t="inlineStr"/>
       <c r="BE85" s="5" t="inlineStr"/>
-      <c r="BF85" s="5" t="inlineStr">
+      <c r="BF85" s="5" t="inlineStr"/>
+      <c r="BG85" s="5" t="inlineStr"/>
+      <c r="BH85" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI85" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG85" s="5" t="inlineStr">
+      <c r="BJ85" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -18155,12 +18761,19 @@
       <c r="BC86" s="3" t="inlineStr"/>
       <c r="BD86" s="3" t="inlineStr"/>
       <c r="BE86" s="3" t="inlineStr"/>
-      <c r="BF86" s="3" t="inlineStr">
+      <c r="BF86" s="3" t="inlineStr"/>
+      <c r="BG86" s="3" t="inlineStr"/>
+      <c r="BH86" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI86" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG86" s="3" t="inlineStr">
+      <c r="BJ86" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -18346,12 +18959,19 @@
       <c r="BC87" s="5" t="inlineStr"/>
       <c r="BD87" s="5" t="inlineStr"/>
       <c r="BE87" s="5" t="inlineStr"/>
-      <c r="BF87" s="5" t="inlineStr">
+      <c r="BF87" s="5" t="inlineStr"/>
+      <c r="BG87" s="5" t="inlineStr"/>
+      <c r="BH87" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI87" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG87" s="5" t="inlineStr">
+      <c r="BJ87" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18545,12 +19165,19 @@
       <c r="BC88" s="3" t="inlineStr"/>
       <c r="BD88" s="3" t="inlineStr"/>
       <c r="BE88" s="3" t="inlineStr"/>
-      <c r="BF88" s="3" t="inlineStr">
+      <c r="BF88" s="3" t="inlineStr"/>
+      <c r="BG88" s="3" t="inlineStr"/>
+      <c r="BH88" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI88" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG88" s="3" t="inlineStr">
+      <c r="BJ88" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18760,12 +19387,19 @@
       <c r="BC89" s="5" t="inlineStr"/>
       <c r="BD89" s="5" t="inlineStr"/>
       <c r="BE89" s="5" t="inlineStr"/>
-      <c r="BF89" s="5" t="inlineStr">
+      <c r="BF89" s="5" t="inlineStr"/>
+      <c r="BG89" s="5" t="inlineStr"/>
+      <c r="BH89" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI89" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG89" s="5" t="inlineStr">
+      <c r="BJ89" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -18975,12 +19609,19 @@
       <c r="BC90" s="3" t="inlineStr"/>
       <c r="BD90" s="3" t="inlineStr"/>
       <c r="BE90" s="3" t="inlineStr"/>
-      <c r="BF90" s="3" t="inlineStr">
+      <c r="BF90" s="3" t="inlineStr"/>
+      <c r="BG90" s="3" t="inlineStr"/>
+      <c r="BH90" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI90" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG90" s="3" t="inlineStr">
+      <c r="BJ90" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -19190,12 +19831,19 @@
       <c r="BC91" s="5" t="inlineStr"/>
       <c r="BD91" s="5" t="inlineStr"/>
       <c r="BE91" s="5" t="inlineStr"/>
-      <c r="BF91" s="5" t="inlineStr">
+      <c r="BF91" s="5" t="inlineStr"/>
+      <c r="BG91" s="5" t="inlineStr"/>
+      <c r="BH91" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI91" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG91" s="5" t="inlineStr">
+      <c r="BJ91" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -19405,12 +20053,19 @@
       <c r="BC92" s="3" t="inlineStr"/>
       <c r="BD92" s="3" t="inlineStr"/>
       <c r="BE92" s="3" t="inlineStr"/>
-      <c r="BF92" s="3" t="inlineStr">
+      <c r="BF92" s="3" t="inlineStr"/>
+      <c r="BG92" s="3" t="inlineStr"/>
+      <c r="BH92" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI92" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG92" s="3" t="inlineStr">
+      <c r="BJ92" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -19604,12 +20259,19 @@
       <c r="BC93" s="5" t="inlineStr"/>
       <c r="BD93" s="5" t="inlineStr"/>
       <c r="BE93" s="5" t="inlineStr"/>
-      <c r="BF93" s="5" t="inlineStr">
+      <c r="BF93" s="5" t="inlineStr"/>
+      <c r="BG93" s="5" t="inlineStr"/>
+      <c r="BH93" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI93" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG93" s="5" t="inlineStr">
+      <c r="BJ93" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -19819,12 +20481,19 @@
       <c r="BC94" s="3" t="inlineStr"/>
       <c r="BD94" s="3" t="inlineStr"/>
       <c r="BE94" s="3" t="inlineStr"/>
-      <c r="BF94" s="3" t="inlineStr">
+      <c r="BF94" s="3" t="inlineStr"/>
+      <c r="BG94" s="3" t="inlineStr"/>
+      <c r="BH94" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI94" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG94" s="3" t="inlineStr">
+      <c r="BJ94" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20034,12 +20703,19 @@
       <c r="BC95" s="5" t="inlineStr"/>
       <c r="BD95" s="5" t="inlineStr"/>
       <c r="BE95" s="5" t="inlineStr"/>
-      <c r="BF95" s="5" t="inlineStr">
+      <c r="BF95" s="5" t="inlineStr"/>
+      <c r="BG95" s="5" t="inlineStr"/>
+      <c r="BH95" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI95" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG95" s="5" t="inlineStr">
+      <c r="BJ95" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20233,12 +20909,19 @@
       <c r="BC96" s="3" t="inlineStr"/>
       <c r="BD96" s="3" t="inlineStr"/>
       <c r="BE96" s="3" t="inlineStr"/>
-      <c r="BF96" s="3" t="inlineStr">
+      <c r="BF96" s="3" t="inlineStr"/>
+      <c r="BG96" s="3" t="inlineStr"/>
+      <c r="BH96" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI96" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG96" s="3" t="inlineStr">
+      <c r="BJ96" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20428,12 +21111,19 @@
       <c r="BC97" s="5" t="inlineStr"/>
       <c r="BD97" s="5" t="inlineStr"/>
       <c r="BE97" s="5" t="inlineStr"/>
-      <c r="BF97" s="5" t="inlineStr">
+      <c r="BF97" s="5" t="inlineStr"/>
+      <c r="BG97" s="5" t="inlineStr"/>
+      <c r="BH97" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI97" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG97" s="5" t="inlineStr">
+      <c r="BJ97" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20643,12 +21333,19 @@
       <c r="BC98" s="3" t="inlineStr"/>
       <c r="BD98" s="3" t="inlineStr"/>
       <c r="BE98" s="3" t="inlineStr"/>
-      <c r="BF98" s="3" t="inlineStr">
+      <c r="BF98" s="3" t="inlineStr"/>
+      <c r="BG98" s="3" t="inlineStr"/>
+      <c r="BH98" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI98" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG98" s="3" t="inlineStr">
+      <c r="BJ98" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20846,12 +21543,19 @@
       <c r="BC99" s="5" t="inlineStr"/>
       <c r="BD99" s="5" t="inlineStr"/>
       <c r="BE99" s="5" t="inlineStr"/>
-      <c r="BF99" s="5" t="inlineStr">
+      <c r="BF99" s="5" t="inlineStr"/>
+      <c r="BG99" s="5" t="inlineStr"/>
+      <c r="BH99" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI99" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG99" s="5" t="inlineStr">
+      <c r="BJ99" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -21033,12 +21737,19 @@
       <c r="BC100" s="3" t="inlineStr"/>
       <c r="BD100" s="3" t="inlineStr"/>
       <c r="BE100" s="3" t="inlineStr"/>
-      <c r="BF100" s="3" t="inlineStr">
+      <c r="BF100" s="3" t="inlineStr"/>
+      <c r="BG100" s="3" t="inlineStr"/>
+      <c r="BH100" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI100" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG100" s="3" t="inlineStr">
+      <c r="BJ100" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21232,12 +21943,19 @@
       <c r="BC101" s="5" t="inlineStr"/>
       <c r="BD101" s="5" t="inlineStr"/>
       <c r="BE101" s="5" t="inlineStr"/>
-      <c r="BF101" s="5" t="inlineStr">
+      <c r="BF101" s="5" t="inlineStr"/>
+      <c r="BG101" s="5" t="inlineStr"/>
+      <c r="BH101" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI101" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG101" s="5" t="inlineStr">
+      <c r="BJ101" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -21443,12 +22161,19 @@
       <c r="BC102" s="3" t="inlineStr"/>
       <c r="BD102" s="3" t="inlineStr"/>
       <c r="BE102" s="3" t="inlineStr"/>
-      <c r="BF102" s="3" t="inlineStr">
+      <c r="BF102" s="3" t="inlineStr"/>
+      <c r="BG102" s="3" t="inlineStr"/>
+      <c r="BH102" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI102" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG102" s="3" t="inlineStr">
+      <c r="BJ102" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21658,12 +22383,19 @@
       <c r="BC103" s="5" t="inlineStr"/>
       <c r="BD103" s="5" t="inlineStr"/>
       <c r="BE103" s="5" t="inlineStr"/>
-      <c r="BF103" s="5" t="inlineStr">
+      <c r="BF103" s="5" t="inlineStr"/>
+      <c r="BG103" s="5" t="inlineStr"/>
+      <c r="BH103" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI103" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG103" s="5" t="inlineStr">
+      <c r="BJ103" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21869,12 +22601,19 @@
       <c r="BC104" s="3" t="inlineStr"/>
       <c r="BD104" s="3" t="inlineStr"/>
       <c r="BE104" s="3" t="inlineStr"/>
-      <c r="BF104" s="3" t="inlineStr">
+      <c r="BF104" s="3" t="inlineStr"/>
+      <c r="BG104" s="3" t="inlineStr"/>
+      <c r="BH104" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI104" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG104" s="3" t="inlineStr">
+      <c r="BJ104" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -22084,12 +22823,19 @@
       <c r="BC105" s="5" t="inlineStr"/>
       <c r="BD105" s="5" t="inlineStr"/>
       <c r="BE105" s="5" t="inlineStr"/>
-      <c r="BF105" s="5" t="inlineStr">
+      <c r="BF105" s="5" t="inlineStr"/>
+      <c r="BG105" s="5" t="inlineStr"/>
+      <c r="BH105" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI105" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG105" s="5" t="inlineStr">
+      <c r="BJ105" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -22279,12 +23025,19 @@
       <c r="BC106" s="3" t="inlineStr"/>
       <c r="BD106" s="3" t="inlineStr"/>
       <c r="BE106" s="3" t="inlineStr"/>
-      <c r="BF106" s="3" t="inlineStr">
+      <c r="BF106" s="3" t="inlineStr"/>
+      <c r="BG106" s="3" t="inlineStr"/>
+      <c r="BH106" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI106" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG106" s="3" t="inlineStr">
+      <c r="BJ106" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22486,12 +23239,19 @@
       <c r="BC107" s="5" t="inlineStr"/>
       <c r="BD107" s="5" t="inlineStr"/>
       <c r="BE107" s="5" t="inlineStr"/>
-      <c r="BF107" s="5" t="inlineStr">
+      <c r="BF107" s="5" t="inlineStr"/>
+      <c r="BG107" s="5" t="inlineStr"/>
+      <c r="BH107" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI107" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG107" s="5" t="inlineStr">
+      <c r="BJ107" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22701,12 +23461,19 @@
       <c r="BC108" s="3" t="inlineStr"/>
       <c r="BD108" s="3" t="inlineStr"/>
       <c r="BE108" s="3" t="inlineStr"/>
-      <c r="BF108" s="3" t="inlineStr">
+      <c r="BF108" s="3" t="inlineStr"/>
+      <c r="BG108" s="3" t="inlineStr"/>
+      <c r="BH108" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI108" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG108" s="3" t="inlineStr">
+      <c r="BJ108" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22896,12 +23663,19 @@
       <c r="BC109" s="5" t="inlineStr"/>
       <c r="BD109" s="5" t="inlineStr"/>
       <c r="BE109" s="5" t="inlineStr"/>
-      <c r="BF109" s="5" t="inlineStr">
+      <c r="BF109" s="5" t="inlineStr"/>
+      <c r="BG109" s="5" t="inlineStr"/>
+      <c r="BH109" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI109" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG109" s="5" t="inlineStr">
+      <c r="BJ109" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23107,12 +23881,19 @@
       <c r="BC110" s="3" t="inlineStr"/>
       <c r="BD110" s="3" t="inlineStr"/>
       <c r="BE110" s="3" t="inlineStr"/>
-      <c r="BF110" s="3" t="inlineStr">
+      <c r="BF110" s="3" t="inlineStr"/>
+      <c r="BG110" s="3" t="inlineStr"/>
+      <c r="BH110" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI110" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG110" s="3" t="inlineStr">
+      <c r="BJ110" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -23322,12 +24103,19 @@
       <c r="BC111" s="5" t="inlineStr"/>
       <c r="BD111" s="5" t="inlineStr"/>
       <c r="BE111" s="5" t="inlineStr"/>
-      <c r="BF111" s="5" t="inlineStr">
+      <c r="BF111" s="5" t="inlineStr"/>
+      <c r="BG111" s="5" t="inlineStr"/>
+      <c r="BH111" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI111" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG111" s="5" t="inlineStr">
+      <c r="BJ111" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23533,12 +24321,19 @@
       <c r="BC112" s="3" t="inlineStr"/>
       <c r="BD112" s="3" t="inlineStr"/>
       <c r="BE112" s="3" t="inlineStr"/>
-      <c r="BF112" s="3" t="inlineStr">
+      <c r="BF112" s="3" t="inlineStr"/>
+      <c r="BG112" s="3" t="inlineStr"/>
+      <c r="BH112" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI112" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG112" s="3" t="inlineStr">
+      <c r="BJ112" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23748,12 +24543,19 @@
       <c r="BC113" s="5" t="inlineStr"/>
       <c r="BD113" s="5" t="inlineStr"/>
       <c r="BE113" s="5" t="inlineStr"/>
-      <c r="BF113" s="5" t="inlineStr">
+      <c r="BF113" s="5" t="inlineStr"/>
+      <c r="BG113" s="5" t="inlineStr"/>
+      <c r="BH113" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI113" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG113" s="5" t="inlineStr">
+      <c r="BJ113" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23961,12 +24763,19 @@
       <c r="BC114" s="3" t="inlineStr"/>
       <c r="BD114" s="3" t="inlineStr"/>
       <c r="BE114" s="3" t="inlineStr"/>
-      <c r="BF114" s="3" t="inlineStr">
+      <c r="BF114" s="3" t="inlineStr"/>
+      <c r="BG114" s="3" t="inlineStr"/>
+      <c r="BH114" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI114" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG114" s="3" t="inlineStr">
+      <c r="BJ114" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24098,12 +24907,19 @@
       <c r="BC115" s="5" t="inlineStr"/>
       <c r="BD115" s="5" t="inlineStr"/>
       <c r="BE115" s="5" t="inlineStr"/>
-      <c r="BF115" s="5" t="inlineStr">
+      <c r="BF115" s="5" t="inlineStr"/>
+      <c r="BG115" s="5" t="inlineStr"/>
+      <c r="BH115" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI115" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG115" s="5" t="inlineStr">
+      <c r="BJ115" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24235,12 +25051,19 @@
       <c r="BC116" s="3" t="inlineStr"/>
       <c r="BD116" s="3" t="inlineStr"/>
       <c r="BE116" s="3" t="inlineStr"/>
-      <c r="BF116" s="3" t="inlineStr">
+      <c r="BF116" s="3" t="inlineStr"/>
+      <c r="BG116" s="3" t="inlineStr"/>
+      <c r="BH116" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI116" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG116" s="3" t="inlineStr">
+      <c r="BJ116" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24372,12 +25195,19 @@
       <c r="BC117" s="5" t="inlineStr"/>
       <c r="BD117" s="5" t="inlineStr"/>
       <c r="BE117" s="5" t="inlineStr"/>
-      <c r="BF117" s="5" t="inlineStr">
+      <c r="BF117" s="5" t="inlineStr"/>
+      <c r="BG117" s="5" t="inlineStr"/>
+      <c r="BH117" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI117" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG117" s="5" t="inlineStr">
+      <c r="BJ117" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24509,12 +25339,19 @@
       <c r="BC118" s="3" t="inlineStr"/>
       <c r="BD118" s="3" t="inlineStr"/>
       <c r="BE118" s="3" t="inlineStr"/>
-      <c r="BF118" s="3" t="inlineStr">
+      <c r="BF118" s="3" t="inlineStr"/>
+      <c r="BG118" s="3" t="inlineStr"/>
+      <c r="BH118" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI118" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG118" s="3" t="inlineStr">
+      <c r="BJ118" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24646,12 +25483,19 @@
       <c r="BC119" s="5" t="inlineStr"/>
       <c r="BD119" s="5" t="inlineStr"/>
       <c r="BE119" s="5" t="inlineStr"/>
-      <c r="BF119" s="5" t="inlineStr">
+      <c r="BF119" s="5" t="inlineStr"/>
+      <c r="BG119" s="5" t="inlineStr"/>
+      <c r="BH119" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI119" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG119" s="5" t="inlineStr">
+      <c r="BJ119" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24783,12 +25627,19 @@
       <c r="BC120" s="3" t="inlineStr"/>
       <c r="BD120" s="3" t="inlineStr"/>
       <c r="BE120" s="3" t="inlineStr"/>
-      <c r="BF120" s="3" t="inlineStr">
+      <c r="BF120" s="3" t="inlineStr"/>
+      <c r="BG120" s="3" t="inlineStr"/>
+      <c r="BH120" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI120" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG120" s="3" t="inlineStr">
+      <c r="BJ120" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24920,12 +25771,19 @@
       <c r="BC121" s="5" t="inlineStr"/>
       <c r="BD121" s="5" t="inlineStr"/>
       <c r="BE121" s="5" t="inlineStr"/>
-      <c r="BF121" s="5" t="inlineStr">
+      <c r="BF121" s="5" t="inlineStr"/>
+      <c r="BG121" s="5" t="inlineStr"/>
+      <c r="BH121" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI121" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG121" s="5" t="inlineStr">
+      <c r="BJ121" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25057,12 +25915,19 @@
       <c r="BC122" s="3" t="inlineStr"/>
       <c r="BD122" s="3" t="inlineStr"/>
       <c r="BE122" s="3" t="inlineStr"/>
-      <c r="BF122" s="3" t="inlineStr">
+      <c r="BF122" s="3" t="inlineStr"/>
+      <c r="BG122" s="3" t="inlineStr"/>
+      <c r="BH122" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI122" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG122" s="3" t="inlineStr">
+      <c r="BJ122" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25194,12 +26059,19 @@
       <c r="BC123" s="5" t="inlineStr"/>
       <c r="BD123" s="5" t="inlineStr"/>
       <c r="BE123" s="5" t="inlineStr"/>
-      <c r="BF123" s="5" t="inlineStr">
+      <c r="BF123" s="5" t="inlineStr"/>
+      <c r="BG123" s="5" t="inlineStr"/>
+      <c r="BH123" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI123" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG123" s="5" t="inlineStr">
+      <c r="BJ123" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -25331,12 +26203,19 @@
       <c r="BC124" s="3" t="inlineStr"/>
       <c r="BD124" s="3" t="inlineStr"/>
       <c r="BE124" s="3" t="inlineStr"/>
-      <c r="BF124" s="3" t="inlineStr">
+      <c r="BF124" s="3" t="inlineStr"/>
+      <c r="BG124" s="3" t="inlineStr"/>
+      <c r="BH124" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI124" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG124" s="3" t="inlineStr">
+      <c r="BJ124" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25468,12 +26347,19 @@
       <c r="BC125" s="5" t="inlineStr"/>
       <c r="BD125" s="5" t="inlineStr"/>
       <c r="BE125" s="5" t="inlineStr"/>
-      <c r="BF125" s="5" t="inlineStr">
+      <c r="BF125" s="5" t="inlineStr"/>
+      <c r="BG125" s="5" t="inlineStr"/>
+      <c r="BH125" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI125" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG125" s="5" t="inlineStr">
+      <c r="BJ125" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -25605,12 +26491,19 @@
       <c r="BC126" s="3" t="inlineStr"/>
       <c r="BD126" s="3" t="inlineStr"/>
       <c r="BE126" s="3" t="inlineStr"/>
-      <c r="BF126" s="3" t="inlineStr">
+      <c r="BF126" s="3" t="inlineStr"/>
+      <c r="BG126" s="3" t="inlineStr"/>
+      <c r="BH126" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI126" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG126" s="3" t="inlineStr">
+      <c r="BJ126" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25742,12 +26635,19 @@
       <c r="BC127" s="5" t="inlineStr"/>
       <c r="BD127" s="5" t="inlineStr"/>
       <c r="BE127" s="5" t="inlineStr"/>
-      <c r="BF127" s="5" t="inlineStr">
+      <c r="BF127" s="5" t="inlineStr"/>
+      <c r="BG127" s="5" t="inlineStr"/>
+      <c r="BH127" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI127" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG127" s="5" t="inlineStr">
+      <c r="BJ127" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25879,12 +26779,19 @@
       <c r="BC128" s="3" t="inlineStr"/>
       <c r="BD128" s="3" t="inlineStr"/>
       <c r="BE128" s="3" t="inlineStr"/>
-      <c r="BF128" s="3" t="inlineStr">
+      <c r="BF128" s="3" t="inlineStr"/>
+      <c r="BG128" s="3" t="inlineStr"/>
+      <c r="BH128" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI128" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG128" s="3" t="inlineStr">
+      <c r="BJ128" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26016,12 +26923,19 @@
       <c r="BC129" s="5" t="inlineStr"/>
       <c r="BD129" s="5" t="inlineStr"/>
       <c r="BE129" s="5" t="inlineStr"/>
-      <c r="BF129" s="5" t="inlineStr">
+      <c r="BF129" s="5" t="inlineStr"/>
+      <c r="BG129" s="5" t="inlineStr"/>
+      <c r="BH129" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI129" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG129" s="5" t="inlineStr">
+      <c r="BJ129" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26153,12 +27067,19 @@
       <c r="BC130" s="3" t="inlineStr"/>
       <c r="BD130" s="3" t="inlineStr"/>
       <c r="BE130" s="3" t="inlineStr"/>
-      <c r="BF130" s="3" t="inlineStr">
+      <c r="BF130" s="3" t="inlineStr"/>
+      <c r="BG130" s="3" t="inlineStr"/>
+      <c r="BH130" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI130" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG130" s="3" t="inlineStr">
+      <c r="BJ130" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26290,12 +27211,19 @@
       <c r="BC131" s="5" t="inlineStr"/>
       <c r="BD131" s="5" t="inlineStr"/>
       <c r="BE131" s="5" t="inlineStr"/>
-      <c r="BF131" s="5" t="inlineStr">
+      <c r="BF131" s="5" t="inlineStr"/>
+      <c r="BG131" s="5" t="inlineStr"/>
+      <c r="BH131" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI131" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG131" s="5" t="inlineStr">
+      <c r="BJ131" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26427,12 +27355,19 @@
       <c r="BC132" s="3" t="inlineStr"/>
       <c r="BD132" s="3" t="inlineStr"/>
       <c r="BE132" s="3" t="inlineStr"/>
-      <c r="BF132" s="3" t="inlineStr">
+      <c r="BF132" s="3" t="inlineStr"/>
+      <c r="BG132" s="3" t="inlineStr"/>
+      <c r="BH132" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI132" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG132" s="3" t="inlineStr">
+      <c r="BJ132" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26564,12 +27499,19 @@
       <c r="BC133" s="5" t="inlineStr"/>
       <c r="BD133" s="5" t="inlineStr"/>
       <c r="BE133" s="5" t="inlineStr"/>
-      <c r="BF133" s="5" t="inlineStr">
+      <c r="BF133" s="5" t="inlineStr"/>
+      <c r="BG133" s="5" t="inlineStr"/>
+      <c r="BH133" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI133" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG133" s="5" t="inlineStr">
+      <c r="BJ133" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26701,12 +27643,19 @@
       <c r="BC134" s="3" t="inlineStr"/>
       <c r="BD134" s="3" t="inlineStr"/>
       <c r="BE134" s="3" t="inlineStr"/>
-      <c r="BF134" s="3" t="inlineStr">
+      <c r="BF134" s="3" t="inlineStr"/>
+      <c r="BG134" s="3" t="inlineStr"/>
+      <c r="BH134" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI134" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG134" s="3" t="inlineStr">
+      <c r="BJ134" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26838,12 +27787,19 @@
       <c r="BC135" s="5" t="inlineStr"/>
       <c r="BD135" s="5" t="inlineStr"/>
       <c r="BE135" s="5" t="inlineStr"/>
-      <c r="BF135" s="5" t="inlineStr">
+      <c r="BF135" s="5" t="inlineStr"/>
+      <c r="BG135" s="5" t="inlineStr"/>
+      <c r="BH135" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI135" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG135" s="5" t="inlineStr">
+      <c r="BJ135" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26975,12 +27931,19 @@
       <c r="BC136" s="3" t="inlineStr"/>
       <c r="BD136" s="3" t="inlineStr"/>
       <c r="BE136" s="3" t="inlineStr"/>
-      <c r="BF136" s="3" t="inlineStr">
+      <c r="BF136" s="3" t="inlineStr"/>
+      <c r="BG136" s="3" t="inlineStr"/>
+      <c r="BH136" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI136" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG136" s="3" t="inlineStr">
+      <c r="BJ136" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -27112,12 +28075,19 @@
       <c r="BC137" s="5" t="inlineStr"/>
       <c r="BD137" s="5" t="inlineStr"/>
       <c r="BE137" s="5" t="inlineStr"/>
-      <c r="BF137" s="5" t="inlineStr">
+      <c r="BF137" s="5" t="inlineStr"/>
+      <c r="BG137" s="5" t="inlineStr"/>
+      <c r="BH137" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI137" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG137" s="5" t="inlineStr">
+      <c r="BJ137" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27249,12 +28219,19 @@
       <c r="BC138" s="3" t="inlineStr"/>
       <c r="BD138" s="3" t="inlineStr"/>
       <c r="BE138" s="3" t="inlineStr"/>
-      <c r="BF138" s="3" t="inlineStr">
+      <c r="BF138" s="3" t="inlineStr"/>
+      <c r="BG138" s="3" t="inlineStr"/>
+      <c r="BH138" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI138" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG138" s="3" t="inlineStr">
+      <c r="BJ138" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27386,12 +28363,19 @@
       <c r="BC139" s="5" t="inlineStr"/>
       <c r="BD139" s="5" t="inlineStr"/>
       <c r="BE139" s="5" t="inlineStr"/>
-      <c r="BF139" s="5" t="inlineStr">
+      <c r="BF139" s="5" t="inlineStr"/>
+      <c r="BG139" s="5" t="inlineStr"/>
+      <c r="BH139" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI139" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG139" s="5" t="inlineStr">
+      <c r="BJ139" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27523,12 +28507,19 @@
       <c r="BC140" s="3" t="inlineStr"/>
       <c r="BD140" s="3" t="inlineStr"/>
       <c r="BE140" s="3" t="inlineStr"/>
-      <c r="BF140" s="3" t="inlineStr">
+      <c r="BF140" s="3" t="inlineStr"/>
+      <c r="BG140" s="3" t="inlineStr"/>
+      <c r="BH140" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI140" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG140" s="3" t="inlineStr">
+      <c r="BJ140" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27732,12 +28723,19 @@
       <c r="BC141" s="5" t="inlineStr"/>
       <c r="BD141" s="5" t="inlineStr"/>
       <c r="BE141" s="5" t="inlineStr"/>
-      <c r="BF141" s="5" t="inlineStr">
+      <c r="BF141" s="5" t="inlineStr"/>
+      <c r="BG141" s="5" t="inlineStr"/>
+      <c r="BH141" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI141" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG141" s="5" t="inlineStr">
+      <c r="BJ141" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27869,12 +28867,19 @@
       <c r="BC142" s="3" t="inlineStr"/>
       <c r="BD142" s="3" t="inlineStr"/>
       <c r="BE142" s="3" t="inlineStr"/>
-      <c r="BF142" s="3" t="inlineStr">
+      <c r="BF142" s="3" t="inlineStr"/>
+      <c r="BG142" s="3" t="inlineStr"/>
+      <c r="BH142" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI142" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG142" s="3" t="inlineStr">
+      <c r="BJ142" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28006,12 +29011,19 @@
       <c r="BC143" s="5" t="inlineStr"/>
       <c r="BD143" s="5" t="inlineStr"/>
       <c r="BE143" s="5" t="inlineStr"/>
-      <c r="BF143" s="5" t="inlineStr">
+      <c r="BF143" s="5" t="inlineStr"/>
+      <c r="BG143" s="5" t="inlineStr"/>
+      <c r="BH143" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI143" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG143" s="5" t="inlineStr">
+      <c r="BJ143" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28143,12 +29155,19 @@
       <c r="BC144" s="3" t="inlineStr"/>
       <c r="BD144" s="3" t="inlineStr"/>
       <c r="BE144" s="3" t="inlineStr"/>
-      <c r="BF144" s="3" t="inlineStr">
+      <c r="BF144" s="3" t="inlineStr"/>
+      <c r="BG144" s="3" t="inlineStr"/>
+      <c r="BH144" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI144" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG144" s="3" t="inlineStr">
+      <c r="BJ144" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28280,12 +29299,19 @@
       <c r="BC145" s="5" t="inlineStr"/>
       <c r="BD145" s="5" t="inlineStr"/>
       <c r="BE145" s="5" t="inlineStr"/>
-      <c r="BF145" s="5" t="inlineStr">
+      <c r="BF145" s="5" t="inlineStr"/>
+      <c r="BG145" s="5" t="inlineStr"/>
+      <c r="BH145" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI145" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG145" s="5" t="inlineStr">
+      <c r="BJ145" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28461,12 +29487,19 @@
       <c r="BC146" s="3" t="inlineStr"/>
       <c r="BD146" s="3" t="inlineStr"/>
       <c r="BE146" s="3" t="inlineStr"/>
-      <c r="BF146" s="3" t="inlineStr">
+      <c r="BF146" s="3" t="inlineStr"/>
+      <c r="BG146" s="3" t="inlineStr"/>
+      <c r="BH146" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI146" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG146" s="3" t="inlineStr">
+      <c r="BJ146" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28598,12 +29631,19 @@
       <c r="BC147" s="5" t="inlineStr"/>
       <c r="BD147" s="5" t="inlineStr"/>
       <c r="BE147" s="5" t="inlineStr"/>
-      <c r="BF147" s="5" t="inlineStr">
+      <c r="BF147" s="5" t="inlineStr"/>
+      <c r="BG147" s="5" t="inlineStr"/>
+      <c r="BH147" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI147" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG147" s="5" t="inlineStr">
+      <c r="BJ147" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28735,12 +29775,19 @@
       <c r="BC148" s="3" t="inlineStr"/>
       <c r="BD148" s="3" t="inlineStr"/>
       <c r="BE148" s="3" t="inlineStr"/>
-      <c r="BF148" s="3" t="inlineStr">
+      <c r="BF148" s="3" t="inlineStr"/>
+      <c r="BG148" s="3" t="inlineStr"/>
+      <c r="BH148" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI148" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG148" s="3" t="inlineStr">
+      <c r="BJ148" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -28872,12 +29919,19 @@
       <c r="BC149" s="5" t="inlineStr"/>
       <c r="BD149" s="5" t="inlineStr"/>
       <c r="BE149" s="5" t="inlineStr"/>
-      <c r="BF149" s="5" t="inlineStr">
+      <c r="BF149" s="5" t="inlineStr"/>
+      <c r="BG149" s="5" t="inlineStr"/>
+      <c r="BH149" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI149" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG149" s="5" t="inlineStr">
+      <c r="BJ149" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29009,12 +30063,19 @@
       <c r="BC150" s="3" t="inlineStr"/>
       <c r="BD150" s="3" t="inlineStr"/>
       <c r="BE150" s="3" t="inlineStr"/>
-      <c r="BF150" s="3" t="inlineStr">
+      <c r="BF150" s="3" t="inlineStr"/>
+      <c r="BG150" s="3" t="inlineStr"/>
+      <c r="BH150" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI150" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG150" s="3" t="inlineStr">
+      <c r="BJ150" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29146,12 +30207,19 @@
       <c r="BC151" s="5" t="inlineStr"/>
       <c r="BD151" s="5" t="inlineStr"/>
       <c r="BE151" s="5" t="inlineStr"/>
-      <c r="BF151" s="5" t="inlineStr">
+      <c r="BF151" s="5" t="inlineStr"/>
+      <c r="BG151" s="5" t="inlineStr"/>
+      <c r="BH151" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI151" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG151" s="5" t="inlineStr">
+      <c r="BJ151" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29283,12 +30351,19 @@
       <c r="BC152" s="3" t="inlineStr"/>
       <c r="BD152" s="3" t="inlineStr"/>
       <c r="BE152" s="3" t="inlineStr"/>
-      <c r="BF152" s="3" t="inlineStr">
+      <c r="BF152" s="3" t="inlineStr"/>
+      <c r="BG152" s="3" t="inlineStr"/>
+      <c r="BH152" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI152" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG152" s="3" t="inlineStr">
+      <c r="BJ152" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29420,12 +30495,19 @@
       <c r="BC153" s="5" t="inlineStr"/>
       <c r="BD153" s="5" t="inlineStr"/>
       <c r="BE153" s="5" t="inlineStr"/>
-      <c r="BF153" s="5" t="inlineStr">
+      <c r="BF153" s="5" t="inlineStr"/>
+      <c r="BG153" s="5" t="inlineStr"/>
+      <c r="BH153" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI153" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG153" s="5" t="inlineStr">
+      <c r="BJ153" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29557,12 +30639,19 @@
       <c r="BC154" s="3" t="inlineStr"/>
       <c r="BD154" s="3" t="inlineStr"/>
       <c r="BE154" s="3" t="inlineStr"/>
-      <c r="BF154" s="3" t="inlineStr">
+      <c r="BF154" s="3" t="inlineStr"/>
+      <c r="BG154" s="3" t="inlineStr"/>
+      <c r="BH154" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI154" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG154" s="3" t="inlineStr">
+      <c r="BJ154" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29694,19 +30783,26 @@
       <c r="BC155" s="5" t="inlineStr"/>
       <c r="BD155" s="5" t="inlineStr"/>
       <c r="BE155" s="5" t="inlineStr"/>
-      <c r="BF155" s="5" t="inlineStr">
+      <c r="BF155" s="5" t="inlineStr"/>
+      <c r="BG155" s="5" t="inlineStr"/>
+      <c r="BH155" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI155" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG155" s="5" t="inlineStr">
+      <c r="BJ155" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29717,7 +30813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG58"/>
+  <dimension ref="A1:BJ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -29779,6 +30875,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -30049,30 +31148,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -30278,12 +31392,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30489,12 +31610,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30700,12 +31828,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30891,12 +32026,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31098,12 +32240,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31309,12 +32458,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31504,12 +32660,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31703,12 +32866,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31894,12 +33064,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -32101,12 +33278,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -32308,12 +33492,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -32499,12 +33690,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -32698,12 +33896,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -32897,12 +34102,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -33104,12 +34316,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -33315,12 +34534,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -33522,12 +34748,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -33733,12 +34966,19 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -33944,12 +35184,19 @@
       <c r="BC20" s="3" t="inlineStr"/>
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr"/>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI20" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BJ20" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -34151,12 +35398,19 @@
       <c r="BC21" s="5" t="inlineStr"/>
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr">
+      <c r="BF21" s="5" t="inlineStr"/>
+      <c r="BG21" s="5" t="inlineStr"/>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG21" s="5" t="inlineStr">
+      <c r="BJ21" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -34358,12 +35612,19 @@
       <c r="BC22" s="3" t="inlineStr"/>
       <c r="BD22" s="3" t="inlineStr"/>
       <c r="BE22" s="3" t="inlineStr"/>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI22" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BJ22" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -34553,12 +35814,19 @@
       <c r="BC23" s="5" t="inlineStr"/>
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr"/>
-      <c r="BF23" s="5" t="inlineStr">
+      <c r="BF23" s="5" t="inlineStr"/>
+      <c r="BG23" s="5" t="inlineStr"/>
+      <c r="BH23" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI23" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG23" s="5" t="inlineStr">
+      <c r="BJ23" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -34764,12 +36032,19 @@
       <c r="BC24" s="3" t="inlineStr"/>
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI24" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BJ24" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -34955,12 +36230,19 @@
       <c r="BC25" s="5" t="inlineStr"/>
       <c r="BD25" s="5" t="inlineStr"/>
       <c r="BE25" s="5" t="inlineStr"/>
-      <c r="BF25" s="5" t="inlineStr">
+      <c r="BF25" s="5" t="inlineStr"/>
+      <c r="BG25" s="5" t="inlineStr"/>
+      <c r="BH25" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI25" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG25" s="5" t="inlineStr">
+      <c r="BJ25" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -35158,12 +36440,19 @@
       <c r="BC26" s="3" t="inlineStr"/>
       <c r="BD26" s="3" t="inlineStr"/>
       <c r="BE26" s="3" t="inlineStr"/>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="3" t="inlineStr"/>
+      <c r="BG26" s="3" t="inlineStr"/>
+      <c r="BH26" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI26" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BJ26" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -35369,12 +36658,19 @@
       <c r="BC27" s="5" t="inlineStr"/>
       <c r="BD27" s="5" t="inlineStr"/>
       <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="5" t="inlineStr"/>
+      <c r="BG27" s="5" t="inlineStr"/>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BJ27" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -35576,12 +36872,19 @@
       <c r="BC28" s="3" t="inlineStr"/>
       <c r="BD28" s="3" t="inlineStr"/>
       <c r="BE28" s="3" t="inlineStr"/>
-      <c r="BF28" s="3" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI28" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG28" s="3" t="inlineStr">
+      <c r="BJ28" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -35787,12 +37090,19 @@
       <c r="BC29" s="5" t="inlineStr"/>
       <c r="BD29" s="5" t="inlineStr"/>
       <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr">
+      <c r="BF29" s="5" t="inlineStr"/>
+      <c r="BG29" s="5" t="inlineStr"/>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG29" s="5" t="inlineStr">
+      <c r="BJ29" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -35978,12 +37288,19 @@
       <c r="BC30" s="3" t="inlineStr"/>
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr"/>
-      <c r="BF30" s="3" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI30" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG30" s="3" t="inlineStr">
+      <c r="BJ30" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -36177,12 +37494,19 @@
       <c r="BC31" s="5" t="inlineStr"/>
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr">
+      <c r="BF31" s="5" t="inlineStr"/>
+      <c r="BG31" s="5" t="inlineStr"/>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG31" s="5" t="inlineStr">
+      <c r="BJ31" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -36356,12 +37680,19 @@
       <c r="BC32" s="3" t="inlineStr"/>
       <c r="BD32" s="3" t="inlineStr"/>
       <c r="BE32" s="3" t="inlineStr"/>
-      <c r="BF32" s="3" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI32" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG32" s="3" t="inlineStr">
+      <c r="BJ32" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -36563,12 +37894,19 @@
       <c r="BC33" s="5" t="inlineStr"/>
       <c r="BD33" s="5" t="inlineStr"/>
       <c r="BE33" s="5" t="inlineStr"/>
-      <c r="BF33" s="5" t="inlineStr">
+      <c r="BF33" s="5" t="inlineStr"/>
+      <c r="BG33" s="5" t="inlineStr"/>
+      <c r="BH33" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI33" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG33" s="5" t="inlineStr">
+      <c r="BJ33" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -36770,12 +38108,19 @@
       <c r="BC34" s="3" t="inlineStr"/>
       <c r="BD34" s="3" t="inlineStr"/>
       <c r="BE34" s="3" t="inlineStr"/>
-      <c r="BF34" s="3" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr"/>
+      <c r="BG34" s="3" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI34" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG34" s="3" t="inlineStr">
+      <c r="BJ34" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -36977,12 +38322,19 @@
       <c r="BC35" s="5" t="inlineStr"/>
       <c r="BD35" s="5" t="inlineStr"/>
       <c r="BE35" s="5" t="inlineStr"/>
-      <c r="BF35" s="5" t="inlineStr">
+      <c r="BF35" s="5" t="inlineStr"/>
+      <c r="BG35" s="5" t="inlineStr"/>
+      <c r="BH35" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI35" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG35" s="5" t="inlineStr">
+      <c r="BJ35" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -37184,12 +38536,19 @@
       <c r="BC36" s="3" t="inlineStr"/>
       <c r="BD36" s="3" t="inlineStr"/>
       <c r="BE36" s="3" t="inlineStr"/>
-      <c r="BF36" s="3" t="inlineStr">
+      <c r="BF36" s="3" t="inlineStr"/>
+      <c r="BG36" s="3" t="inlineStr"/>
+      <c r="BH36" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI36" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG36" s="3" t="inlineStr">
+      <c r="BJ36" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -37395,12 +38754,19 @@
       <c r="BC37" s="5" t="inlineStr"/>
       <c r="BD37" s="5" t="inlineStr"/>
       <c r="BE37" s="5" t="inlineStr"/>
-      <c r="BF37" s="5" t="inlineStr">
+      <c r="BF37" s="5" t="inlineStr"/>
+      <c r="BG37" s="5" t="inlineStr"/>
+      <c r="BH37" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI37" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG37" s="5" t="inlineStr">
+      <c r="BJ37" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -37606,12 +38972,19 @@
       <c r="BC38" s="3" t="inlineStr"/>
       <c r="BD38" s="3" t="inlineStr"/>
       <c r="BE38" s="3" t="inlineStr"/>
-      <c r="BF38" s="3" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr"/>
+      <c r="BG38" s="3" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI38" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG38" s="3" t="inlineStr">
+      <c r="BJ38" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -37809,12 +39182,19 @@
       <c r="BC39" s="5" t="inlineStr"/>
       <c r="BD39" s="5" t="inlineStr"/>
       <c r="BE39" s="5" t="inlineStr"/>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="5" t="inlineStr"/>
+      <c r="BG39" s="5" t="inlineStr"/>
+      <c r="BH39" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI39" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr">
+      <c r="BJ39" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -38000,12 +39380,19 @@
       <c r="BC40" s="3" t="inlineStr"/>
       <c r="BD40" s="3" t="inlineStr"/>
       <c r="BE40" s="3" t="inlineStr"/>
-      <c r="BF40" s="3" t="inlineStr">
+      <c r="BF40" s="3" t="inlineStr"/>
+      <c r="BG40" s="3" t="inlineStr"/>
+      <c r="BH40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI40" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG40" s="3" t="inlineStr">
+      <c r="BJ40" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -38199,12 +39586,19 @@
       <c r="BC41" s="5" t="inlineStr"/>
       <c r="BD41" s="5" t="inlineStr"/>
       <c r="BE41" s="5" t="inlineStr"/>
-      <c r="BF41" s="5" t="inlineStr">
+      <c r="BF41" s="5" t="inlineStr"/>
+      <c r="BG41" s="5" t="inlineStr"/>
+      <c r="BH41" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI41" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG41" s="5" t="inlineStr">
+      <c r="BJ41" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -38410,12 +39804,19 @@
       <c r="BC42" s="3" t="inlineStr"/>
       <c r="BD42" s="3" t="inlineStr"/>
       <c r="BE42" s="3" t="inlineStr"/>
-      <c r="BF42" s="3" t="inlineStr">
+      <c r="BF42" s="3" t="inlineStr"/>
+      <c r="BG42" s="3" t="inlineStr"/>
+      <c r="BH42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI42" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG42" s="3" t="inlineStr">
+      <c r="BJ42" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -38609,12 +40010,19 @@
       <c r="BC43" s="5" t="inlineStr"/>
       <c r="BD43" s="5" t="inlineStr"/>
       <c r="BE43" s="5" t="inlineStr"/>
-      <c r="BF43" s="5" t="inlineStr">
+      <c r="BF43" s="5" t="inlineStr"/>
+      <c r="BG43" s="5" t="inlineStr"/>
+      <c r="BH43" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI43" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG43" s="5" t="inlineStr">
+      <c r="BJ43" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -38808,12 +40216,19 @@
       <c r="BC44" s="3" t="inlineStr"/>
       <c r="BD44" s="3" t="inlineStr"/>
       <c r="BE44" s="3" t="inlineStr"/>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="3" t="inlineStr"/>
+      <c r="BG44" s="3" t="inlineStr"/>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI44" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BJ44" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -39007,12 +40422,19 @@
       <c r="BC45" s="5" t="inlineStr"/>
       <c r="BD45" s="5" t="inlineStr"/>
       <c r="BE45" s="5" t="inlineStr"/>
-      <c r="BF45" s="5" t="inlineStr">
+      <c r="BF45" s="5" t="inlineStr"/>
+      <c r="BG45" s="5" t="inlineStr"/>
+      <c r="BH45" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI45" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG45" s="5" t="inlineStr">
+      <c r="BJ45" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -39198,12 +40620,19 @@
       <c r="BC46" s="3" t="inlineStr"/>
       <c r="BD46" s="3" t="inlineStr"/>
       <c r="BE46" s="3" t="inlineStr"/>
-      <c r="BF46" s="3" t="inlineStr">
+      <c r="BF46" s="3" t="inlineStr"/>
+      <c r="BG46" s="3" t="inlineStr"/>
+      <c r="BH46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI46" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG46" s="3" t="inlineStr">
+      <c r="BJ46" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -39409,12 +40838,19 @@
       <c r="BC47" s="5" t="inlineStr"/>
       <c r="BD47" s="5" t="inlineStr"/>
       <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr">
+      <c r="BF47" s="5" t="inlineStr"/>
+      <c r="BG47" s="5" t="inlineStr"/>
+      <c r="BH47" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI47" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG47" s="5" t="inlineStr">
+      <c r="BJ47" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -39596,12 +41032,19 @@
       <c r="BC48" s="3" t="inlineStr"/>
       <c r="BD48" s="3" t="inlineStr"/>
       <c r="BE48" s="3" t="inlineStr"/>
-      <c r="BF48" s="3" t="inlineStr">
+      <c r="BF48" s="3" t="inlineStr"/>
+      <c r="BG48" s="3" t="inlineStr"/>
+      <c r="BH48" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI48" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BJ48" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -39779,12 +41222,19 @@
       <c r="BC49" s="5" t="inlineStr"/>
       <c r="BD49" s="5" t="inlineStr"/>
       <c r="BE49" s="5" t="inlineStr"/>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="5" t="inlineStr"/>
+      <c r="BG49" s="5" t="inlineStr"/>
+      <c r="BH49" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI49" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BJ49" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -39990,12 +41440,19 @@
       <c r="BC50" s="3" t="inlineStr"/>
       <c r="BD50" s="3" t="inlineStr"/>
       <c r="BE50" s="3" t="inlineStr"/>
-      <c r="BF50" s="3" t="inlineStr">
+      <c r="BF50" s="3" t="inlineStr"/>
+      <c r="BG50" s="3" t="inlineStr"/>
+      <c r="BH50" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI50" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG50" s="3" t="inlineStr">
+      <c r="BJ50" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -40197,12 +41654,19 @@
       <c r="BC51" s="5" t="inlineStr"/>
       <c r="BD51" s="5" t="inlineStr"/>
       <c r="BE51" s="5" t="inlineStr"/>
-      <c r="BF51" s="5" t="inlineStr">
+      <c r="BF51" s="5" t="inlineStr"/>
+      <c r="BG51" s="5" t="inlineStr"/>
+      <c r="BH51" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI51" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG51" s="5" t="inlineStr">
+      <c r="BJ51" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -40400,12 +41864,19 @@
       <c r="BC52" s="3" t="inlineStr"/>
       <c r="BD52" s="3" t="inlineStr"/>
       <c r="BE52" s="3" t="inlineStr"/>
-      <c r="BF52" s="3" t="inlineStr">
+      <c r="BF52" s="3" t="inlineStr"/>
+      <c r="BG52" s="3" t="inlineStr"/>
+      <c r="BH52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI52" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG52" s="3" t="inlineStr">
+      <c r="BJ52" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -40611,12 +42082,19 @@
       <c r="BC53" s="5" t="inlineStr"/>
       <c r="BD53" s="5" t="inlineStr"/>
       <c r="BE53" s="5" t="inlineStr"/>
-      <c r="BF53" s="5" t="inlineStr">
+      <c r="BF53" s="5" t="inlineStr"/>
+      <c r="BG53" s="5" t="inlineStr"/>
+      <c r="BH53" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI53" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG53" s="5" t="inlineStr">
+      <c r="BJ53" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -40806,12 +42284,19 @@
       <c r="BC54" s="3" t="inlineStr"/>
       <c r="BD54" s="3" t="inlineStr"/>
       <c r="BE54" s="3" t="inlineStr"/>
-      <c r="BF54" s="3" t="inlineStr">
+      <c r="BF54" s="3" t="inlineStr"/>
+      <c r="BG54" s="3" t="inlineStr"/>
+      <c r="BH54" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI54" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG54" s="3" t="inlineStr">
+      <c r="BJ54" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -41017,12 +42502,19 @@
       <c r="BC55" s="5" t="inlineStr"/>
       <c r="BD55" s="5" t="inlineStr"/>
       <c r="BE55" s="5" t="inlineStr"/>
-      <c r="BF55" s="5" t="inlineStr">
+      <c r="BF55" s="5" t="inlineStr"/>
+      <c r="BG55" s="5" t="inlineStr"/>
+      <c r="BH55" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI55" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG55" s="5" t="inlineStr">
+      <c r="BJ55" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -41204,12 +42696,19 @@
       <c r="BC56" s="3" t="inlineStr"/>
       <c r="BD56" s="3" t="inlineStr"/>
       <c r="BE56" s="3" t="inlineStr"/>
-      <c r="BF56" s="3" t="inlineStr">
+      <c r="BF56" s="3" t="inlineStr"/>
+      <c r="BG56" s="3" t="inlineStr"/>
+      <c r="BH56" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI56" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG56" s="3" t="inlineStr">
+      <c r="BJ56" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -41411,12 +42910,19 @@
       <c r="BC57" s="5" t="inlineStr"/>
       <c r="BD57" s="5" t="inlineStr"/>
       <c r="BE57" s="5" t="inlineStr"/>
-      <c r="BF57" s="5" t="inlineStr">
+      <c r="BF57" s="5" t="inlineStr"/>
+      <c r="BG57" s="5" t="inlineStr"/>
+      <c r="BH57" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI57" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG57" s="5" t="inlineStr">
+      <c r="BJ57" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -41614,19 +43120,26 @@
       <c r="BC58" s="3" t="inlineStr"/>
       <c r="BD58" s="3" t="inlineStr"/>
       <c r="BE58" s="3" t="inlineStr"/>
-      <c r="BF58" s="3" t="inlineStr">
+      <c r="BF58" s="3" t="inlineStr"/>
+      <c r="BG58" s="3" t="inlineStr"/>
+      <c r="BH58" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI58" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BJ58" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41637,7 +43150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG19"/>
+  <dimension ref="A1:BJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -41699,6 +43212,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -41969,30 +43485,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -42198,12 +43729,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -42393,12 +43931,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -42608,12 +44153,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -42823,12 +44375,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -43038,12 +44597,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -43253,12 +44819,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -43468,12 +45041,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -43683,12 +45263,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -43886,12 +45473,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -44101,12 +45695,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -44300,12 +45901,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -44491,12 +46099,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -44706,12 +46321,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -44897,12 +46519,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -45112,12 +46741,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -45303,12 +46939,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -45518,12 +47161,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -45733,19 +47383,26 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45756,7 +47413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG16"/>
+  <dimension ref="A1:BJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -45818,6 +47475,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -46088,30 +47748,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -46293,12 +47968,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -46504,12 +48186,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -46703,12 +48392,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -46918,12 +48614,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -47117,12 +48820,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -47312,12 +49022,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -47523,12 +49240,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -47706,12 +49430,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -47921,12 +49652,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -48112,12 +49850,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -48303,12 +50048,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -48502,12 +50254,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -48717,12 +50476,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -48932,12 +50698,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -49147,19 +50920,26 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49170,7 +50950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG65"/>
+  <dimension ref="A1:BJ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -49232,6 +51012,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -49502,30 +51285,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -49735,12 +51533,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -49934,12 +51739,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -50149,12 +51961,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -50364,12 +52183,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -50563,12 +52389,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -50758,12 +52591,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -50973,12 +52813,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -51176,12 +53023,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -51363,12 +53217,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -51562,12 +53423,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -51773,12 +53641,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -51988,12 +53863,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -52199,12 +54081,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -52414,12 +54303,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -52609,12 +54505,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -52816,12 +54719,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -53031,12 +54941,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -53226,12 +55143,19 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -53437,12 +55361,19 @@
       <c r="BC20" s="3" t="inlineStr"/>
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr"/>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI20" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BJ20" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -53652,12 +55583,19 @@
       <c r="BC21" s="5" t="inlineStr"/>
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr">
+      <c r="BF21" s="5" t="inlineStr"/>
+      <c r="BG21" s="5" t="inlineStr"/>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG21" s="5" t="inlineStr">
+      <c r="BJ21" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -53863,12 +55801,19 @@
       <c r="BC22" s="3" t="inlineStr"/>
       <c r="BD22" s="3" t="inlineStr"/>
       <c r="BE22" s="3" t="inlineStr"/>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI22" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BJ22" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -54078,12 +56023,19 @@
       <c r="BC23" s="5" t="inlineStr"/>
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr"/>
-      <c r="BF23" s="5" t="inlineStr">
+      <c r="BF23" s="5" t="inlineStr"/>
+      <c r="BG23" s="5" t="inlineStr"/>
+      <c r="BH23" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI23" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG23" s="5" t="inlineStr">
+      <c r="BJ23" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -54291,12 +56243,19 @@
       <c r="BC24" s="3" t="inlineStr"/>
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI24" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BJ24" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -54428,12 +56387,19 @@
       <c r="BC25" s="5" t="inlineStr"/>
       <c r="BD25" s="5" t="inlineStr"/>
       <c r="BE25" s="5" t="inlineStr"/>
-      <c r="BF25" s="5" t="inlineStr">
+      <c r="BF25" s="5" t="inlineStr"/>
+      <c r="BG25" s="5" t="inlineStr"/>
+      <c r="BH25" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI25" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG25" s="5" t="inlineStr">
+      <c r="BJ25" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -54565,12 +56531,19 @@
       <c r="BC26" s="3" t="inlineStr"/>
       <c r="BD26" s="3" t="inlineStr"/>
       <c r="BE26" s="3" t="inlineStr"/>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="3" t="inlineStr"/>
+      <c r="BG26" s="3" t="inlineStr"/>
+      <c r="BH26" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI26" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BJ26" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -54702,12 +56675,19 @@
       <c r="BC27" s="5" t="inlineStr"/>
       <c r="BD27" s="5" t="inlineStr"/>
       <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="5" t="inlineStr"/>
+      <c r="BG27" s="5" t="inlineStr"/>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BJ27" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -54839,12 +56819,19 @@
       <c r="BC28" s="3" t="inlineStr"/>
       <c r="BD28" s="3" t="inlineStr"/>
       <c r="BE28" s="3" t="inlineStr"/>
-      <c r="BF28" s="3" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI28" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG28" s="3" t="inlineStr">
+      <c r="BJ28" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -54976,12 +56963,19 @@
       <c r="BC29" s="5" t="inlineStr"/>
       <c r="BD29" s="5" t="inlineStr"/>
       <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr">
+      <c r="BF29" s="5" t="inlineStr"/>
+      <c r="BG29" s="5" t="inlineStr"/>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG29" s="5" t="inlineStr">
+      <c r="BJ29" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -55113,12 +57107,19 @@
       <c r="BC30" s="3" t="inlineStr"/>
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr"/>
-      <c r="BF30" s="3" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI30" s="3" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG30" s="3" t="inlineStr">
+      <c r="BJ30" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -55250,12 +57251,19 @@
       <c r="BC31" s="5" t="inlineStr"/>
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr">
+      <c r="BF31" s="5" t="inlineStr"/>
+      <c r="BG31" s="5" t="inlineStr"/>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG31" s="5" t="inlineStr">
+      <c r="BJ31" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -55387,12 +57395,19 @@
       <c r="BC32" s="3" t="inlineStr"/>
       <c r="BD32" s="3" t="inlineStr"/>
       <c r="BE32" s="3" t="inlineStr"/>
-      <c r="BF32" s="3" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI32" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG32" s="3" t="inlineStr">
+      <c r="BJ32" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -55524,12 +57539,19 @@
       <c r="BC33" s="5" t="inlineStr"/>
       <c r="BD33" s="5" t="inlineStr"/>
       <c r="BE33" s="5" t="inlineStr"/>
-      <c r="BF33" s="5" t="inlineStr">
+      <c r="BF33" s="5" t="inlineStr"/>
+      <c r="BG33" s="5" t="inlineStr"/>
+      <c r="BH33" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI33" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG33" s="5" t="inlineStr">
+      <c r="BJ33" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -55661,12 +57683,19 @@
       <c r="BC34" s="3" t="inlineStr"/>
       <c r="BD34" s="3" t="inlineStr"/>
       <c r="BE34" s="3" t="inlineStr"/>
-      <c r="BF34" s="3" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr"/>
+      <c r="BG34" s="3" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI34" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG34" s="3" t="inlineStr">
+      <c r="BJ34" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -55798,12 +57827,19 @@
       <c r="BC35" s="5" t="inlineStr"/>
       <c r="BD35" s="5" t="inlineStr"/>
       <c r="BE35" s="5" t="inlineStr"/>
-      <c r="BF35" s="5" t="inlineStr">
+      <c r="BF35" s="5" t="inlineStr"/>
+      <c r="BG35" s="5" t="inlineStr"/>
+      <c r="BH35" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI35" s="5" t="inlineStr">
         <is>
           <t>1.012</t>
         </is>
       </c>
-      <c r="BG35" s="5" t="inlineStr">
+      <c r="BJ35" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, reb: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -55935,12 +57971,19 @@
       <c r="BC36" s="3" t="inlineStr"/>
       <c r="BD36" s="3" t="inlineStr"/>
       <c r="BE36" s="3" t="inlineStr"/>
-      <c r="BF36" s="3" t="inlineStr">
+      <c r="BF36" s="3" t="inlineStr"/>
+      <c r="BG36" s="3" t="inlineStr"/>
+      <c r="BH36" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI36" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG36" s="3" t="inlineStr">
+      <c r="BJ36" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -56072,12 +58115,19 @@
       <c r="BC37" s="5" t="inlineStr"/>
       <c r="BD37" s="5" t="inlineStr"/>
       <c r="BE37" s="5" t="inlineStr"/>
-      <c r="BF37" s="5" t="inlineStr">
+      <c r="BF37" s="5" t="inlineStr"/>
+      <c r="BG37" s="5" t="inlineStr"/>
+      <c r="BH37" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI37" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG37" s="5" t="inlineStr">
+      <c r="BJ37" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -56209,12 +58259,19 @@
       <c r="BC38" s="3" t="inlineStr"/>
       <c r="BD38" s="3" t="inlineStr"/>
       <c r="BE38" s="3" t="inlineStr"/>
-      <c r="BF38" s="3" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr"/>
+      <c r="BG38" s="3" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI38" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG38" s="3" t="inlineStr">
+      <c r="BJ38" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -56346,12 +58403,19 @@
       <c r="BC39" s="5" t="inlineStr"/>
       <c r="BD39" s="5" t="inlineStr"/>
       <c r="BE39" s="5" t="inlineStr"/>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="5" t="inlineStr"/>
+      <c r="BG39" s="5" t="inlineStr"/>
+      <c r="BH39" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI39" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr">
+      <c r="BJ39" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -56483,12 +58547,19 @@
       <c r="BC40" s="3" t="inlineStr"/>
       <c r="BD40" s="3" t="inlineStr"/>
       <c r="BE40" s="3" t="inlineStr"/>
-      <c r="BF40" s="3" t="inlineStr">
+      <c r="BF40" s="3" t="inlineStr"/>
+      <c r="BG40" s="3" t="inlineStr"/>
+      <c r="BH40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI40" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG40" s="3" t="inlineStr">
+      <c r="BJ40" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ast: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -56620,12 +58691,19 @@
       <c r="BC41" s="5" t="inlineStr"/>
       <c r="BD41" s="5" t="inlineStr"/>
       <c r="BE41" s="5" t="inlineStr"/>
-      <c r="BF41" s="5" t="inlineStr">
+      <c r="BF41" s="5" t="inlineStr"/>
+      <c r="BG41" s="5" t="inlineStr"/>
+      <c r="BH41" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI41" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG41" s="5" t="inlineStr">
+      <c r="BJ41" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -56757,12 +58835,19 @@
       <c r="BC42" s="3" t="inlineStr"/>
       <c r="BD42" s="3" t="inlineStr"/>
       <c r="BE42" s="3" t="inlineStr"/>
-      <c r="BF42" s="3" t="inlineStr">
+      <c r="BF42" s="3" t="inlineStr"/>
+      <c r="BG42" s="3" t="inlineStr"/>
+      <c r="BH42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI42" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG42" s="3" t="inlineStr">
+      <c r="BJ42" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -56894,12 +58979,19 @@
       <c r="BC43" s="5" t="inlineStr"/>
       <c r="BD43" s="5" t="inlineStr"/>
       <c r="BE43" s="5" t="inlineStr"/>
-      <c r="BF43" s="5" t="inlineStr">
+      <c r="BF43" s="5" t="inlineStr"/>
+      <c r="BG43" s="5" t="inlineStr"/>
+      <c r="BH43" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI43" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG43" s="5" t="inlineStr">
+      <c r="BJ43" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57031,12 +59123,19 @@
       <c r="BC44" s="3" t="inlineStr"/>
       <c r="BD44" s="3" t="inlineStr"/>
       <c r="BE44" s="3" t="inlineStr"/>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="3" t="inlineStr"/>
+      <c r="BG44" s="3" t="inlineStr"/>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI44" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BJ44" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57168,12 +59267,19 @@
       <c r="BC45" s="5" t="inlineStr"/>
       <c r="BD45" s="5" t="inlineStr"/>
       <c r="BE45" s="5" t="inlineStr"/>
-      <c r="BF45" s="5" t="inlineStr">
+      <c r="BF45" s="5" t="inlineStr"/>
+      <c r="BG45" s="5" t="inlineStr"/>
+      <c r="BH45" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI45" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG45" s="5" t="inlineStr">
+      <c r="BJ45" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57305,12 +59411,19 @@
       <c r="BC46" s="3" t="inlineStr"/>
       <c r="BD46" s="3" t="inlineStr"/>
       <c r="BE46" s="3" t="inlineStr"/>
-      <c r="BF46" s="3" t="inlineStr">
+      <c r="BF46" s="3" t="inlineStr"/>
+      <c r="BG46" s="3" t="inlineStr"/>
+      <c r="BH46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI46" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG46" s="3" t="inlineStr">
+      <c r="BJ46" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -57442,12 +59555,19 @@
       <c r="BC47" s="5" t="inlineStr"/>
       <c r="BD47" s="5" t="inlineStr"/>
       <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr">
+      <c r="BF47" s="5" t="inlineStr"/>
+      <c r="BG47" s="5" t="inlineStr"/>
+      <c r="BH47" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI47" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG47" s="5" t="inlineStr">
+      <c r="BJ47" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57579,12 +59699,19 @@
       <c r="BC48" s="3" t="inlineStr"/>
       <c r="BD48" s="3" t="inlineStr"/>
       <c r="BE48" s="3" t="inlineStr"/>
-      <c r="BF48" s="3" t="inlineStr">
+      <c r="BF48" s="3" t="inlineStr"/>
+      <c r="BG48" s="3" t="inlineStr"/>
+      <c r="BH48" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI48" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BJ48" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57716,12 +59843,19 @@
       <c r="BC49" s="5" t="inlineStr"/>
       <c r="BD49" s="5" t="inlineStr"/>
       <c r="BE49" s="5" t="inlineStr"/>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="5" t="inlineStr"/>
+      <c r="BG49" s="5" t="inlineStr"/>
+      <c r="BH49" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI49" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BJ49" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -57853,12 +59987,19 @@
       <c r="BC50" s="3" t="inlineStr"/>
       <c r="BD50" s="3" t="inlineStr"/>
       <c r="BE50" s="3" t="inlineStr"/>
-      <c r="BF50" s="3" t="inlineStr">
+      <c r="BF50" s="3" t="inlineStr"/>
+      <c r="BG50" s="3" t="inlineStr"/>
+      <c r="BH50" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI50" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG50" s="3" t="inlineStr">
+      <c r="BJ50" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58062,12 +60203,19 @@
       <c r="BC51" s="5" t="inlineStr"/>
       <c r="BD51" s="5" t="inlineStr"/>
       <c r="BE51" s="5" t="inlineStr"/>
-      <c r="BF51" s="5" t="inlineStr">
+      <c r="BF51" s="5" t="inlineStr"/>
+      <c r="BG51" s="5" t="inlineStr"/>
+      <c r="BH51" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI51" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG51" s="5" t="inlineStr">
+      <c r="BJ51" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58199,12 +60347,19 @@
       <c r="BC52" s="3" t="inlineStr"/>
       <c r="BD52" s="3" t="inlineStr"/>
       <c r="BE52" s="3" t="inlineStr"/>
-      <c r="BF52" s="3" t="inlineStr">
+      <c r="BF52" s="3" t="inlineStr"/>
+      <c r="BG52" s="3" t="inlineStr"/>
+      <c r="BH52" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI52" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG52" s="3" t="inlineStr">
+      <c r="BJ52" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58336,12 +60491,19 @@
       <c r="BC53" s="5" t="inlineStr"/>
       <c r="BD53" s="5" t="inlineStr"/>
       <c r="BE53" s="5" t="inlineStr"/>
-      <c r="BF53" s="5" t="inlineStr">
+      <c r="BF53" s="5" t="inlineStr"/>
+      <c r="BG53" s="5" t="inlineStr"/>
+      <c r="BH53" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI53" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG53" s="5" t="inlineStr">
+      <c r="BJ53" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58473,12 +60635,19 @@
       <c r="BC54" s="3" t="inlineStr"/>
       <c r="BD54" s="3" t="inlineStr"/>
       <c r="BE54" s="3" t="inlineStr"/>
-      <c r="BF54" s="3" t="inlineStr">
+      <c r="BF54" s="3" t="inlineStr"/>
+      <c r="BG54" s="3" t="inlineStr"/>
+      <c r="BH54" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI54" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG54" s="3" t="inlineStr">
+      <c r="BJ54" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58610,12 +60779,19 @@
       <c r="BC55" s="5" t="inlineStr"/>
       <c r="BD55" s="5" t="inlineStr"/>
       <c r="BE55" s="5" t="inlineStr"/>
-      <c r="BF55" s="5" t="inlineStr">
+      <c r="BF55" s="5" t="inlineStr"/>
+      <c r="BG55" s="5" t="inlineStr"/>
+      <c r="BH55" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI55" s="5" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG55" s="5" t="inlineStr">
+      <c r="BJ55" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58791,12 +60967,19 @@
       <c r="BC56" s="3" t="inlineStr"/>
       <c r="BD56" s="3" t="inlineStr"/>
       <c r="BE56" s="3" t="inlineStr"/>
-      <c r="BF56" s="3" t="inlineStr">
+      <c r="BF56" s="3" t="inlineStr"/>
+      <c r="BG56" s="3" t="inlineStr"/>
+      <c r="BH56" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI56" s="3" t="inlineStr">
         <is>
           <t>0.958</t>
         </is>
       </c>
-      <c r="BG56" s="3" t="inlineStr">
+      <c r="BJ56" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, reb: 0.96x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -58928,12 +61111,19 @@
       <c r="BC57" s="5" t="inlineStr"/>
       <c r="BD57" s="5" t="inlineStr"/>
       <c r="BE57" s="5" t="inlineStr"/>
-      <c r="BF57" s="5" t="inlineStr">
+      <c r="BF57" s="5" t="inlineStr"/>
+      <c r="BG57" s="5" t="inlineStr"/>
+      <c r="BH57" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI57" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG57" s="5" t="inlineStr">
+      <c r="BJ57" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ast: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -59065,12 +61255,19 @@
       <c r="BC58" s="3" t="inlineStr"/>
       <c r="BD58" s="3" t="inlineStr"/>
       <c r="BE58" s="3" t="inlineStr"/>
-      <c r="BF58" s="3" t="inlineStr">
+      <c r="BF58" s="3" t="inlineStr"/>
+      <c r="BG58" s="3" t="inlineStr"/>
+      <c r="BH58" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI58" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BJ58" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -59202,12 +61399,19 @@
       <c r="BC59" s="5" t="inlineStr"/>
       <c r="BD59" s="5" t="inlineStr"/>
       <c r="BE59" s="5" t="inlineStr"/>
-      <c r="BF59" s="5" t="inlineStr">
+      <c r="BF59" s="5" t="inlineStr"/>
+      <c r="BG59" s="5" t="inlineStr"/>
+      <c r="BH59" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI59" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG59" s="5" t="inlineStr">
+      <c r="BJ59" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -59339,12 +61543,19 @@
       <c r="BC60" s="3" t="inlineStr"/>
       <c r="BD60" s="3" t="inlineStr"/>
       <c r="BE60" s="3" t="inlineStr"/>
-      <c r="BF60" s="3" t="inlineStr">
+      <c r="BF60" s="3" t="inlineStr"/>
+      <c r="BG60" s="3" t="inlineStr"/>
+      <c r="BH60" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI60" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG60" s="3" t="inlineStr">
+      <c r="BJ60" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -59476,12 +61687,19 @@
       <c r="BC61" s="5" t="inlineStr"/>
       <c r="BD61" s="5" t="inlineStr"/>
       <c r="BE61" s="5" t="inlineStr"/>
-      <c r="BF61" s="5" t="inlineStr">
+      <c r="BF61" s="5" t="inlineStr"/>
+      <c r="BG61" s="5" t="inlineStr"/>
+      <c r="BH61" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI61" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG61" s="5" t="inlineStr">
+      <c r="BJ61" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -59613,12 +61831,19 @@
       <c r="BC62" s="3" t="inlineStr"/>
       <c r="BD62" s="3" t="inlineStr"/>
       <c r="BE62" s="3" t="inlineStr"/>
-      <c r="BF62" s="3" t="inlineStr">
+      <c r="BF62" s="3" t="inlineStr"/>
+      <c r="BG62" s="3" t="inlineStr"/>
+      <c r="BH62" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI62" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG62" s="3" t="inlineStr">
+      <c r="BJ62" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -59750,12 +61975,19 @@
       <c r="BC63" s="5" t="inlineStr"/>
       <c r="BD63" s="5" t="inlineStr"/>
       <c r="BE63" s="5" t="inlineStr"/>
-      <c r="BF63" s="5" t="inlineStr">
+      <c r="BF63" s="5" t="inlineStr"/>
+      <c r="BG63" s="5" t="inlineStr"/>
+      <c r="BH63" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI63" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG63" s="5" t="inlineStr">
+      <c r="BJ63" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -59887,12 +62119,19 @@
       <c r="BC64" s="3" t="inlineStr"/>
       <c r="BD64" s="3" t="inlineStr"/>
       <c r="BE64" s="3" t="inlineStr"/>
-      <c r="BF64" s="3" t="inlineStr">
+      <c r="BF64" s="3" t="inlineStr"/>
+      <c r="BG64" s="3" t="inlineStr"/>
+      <c r="BH64" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI64" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG64" s="3" t="inlineStr">
+      <c r="BJ64" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -60024,19 +62263,26 @@
       <c r="BC65" s="5" t="inlineStr"/>
       <c r="BD65" s="5" t="inlineStr"/>
       <c r="BE65" s="5" t="inlineStr"/>
-      <c r="BF65" s="5" t="inlineStr">
+      <c r="BF65" s="5" t="inlineStr"/>
+      <c r="BG65" s="5" t="inlineStr"/>
+      <c r="BH65" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI65" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG65" s="5" t="inlineStr">
+      <c r="BJ65" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NBA/step8_nba1q_direction_clean.xlsx
+++ b/NBA/step8_nba1q_direction_clean.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ211"/>
+  <dimension ref="A1:BJ212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -37502,7 +37502,7 @@
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
@@ -43274,24 +43274,24 @@
       <c r="B207" s="5" t="inlineStr"/>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
           <t>2026-04-30 21:30:00-04:00</t>
@@ -43317,30 +43317,46 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L207" s="5" t="inlineStr"/>
-      <c r="M207" s="5" t="inlineStr"/>
+      <c r="L207" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N207" s="5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O207" s="5" t="n">
-        <v>0.8335</v>
+        <v>0.8636</v>
       </c>
       <c r="P207" s="5" t="inlineStr"/>
       <c r="Q207" s="5" t="inlineStr"/>
-      <c r="R207" s="5" t="inlineStr"/>
-      <c r="S207" s="5" t="inlineStr"/>
-      <c r="T207" s="5" t="inlineStr"/>
-      <c r="U207" s="5" t="inlineStr"/>
-      <c r="V207" s="5" t="inlineStr"/>
-      <c r="W207" s="5" t="inlineStr"/>
+      <c r="R207" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S207" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T207" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U207" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V207" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W207" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="X207" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y207" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z207" s="5" t="inlineStr">
@@ -43355,34 +43371,90 @@
       </c>
       <c r="AB207" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AC207" s="5" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AD207" s="5" t="inlineStr"/>
-      <c r="AE207" s="5" t="inlineStr"/>
-      <c r="AF207" s="5" t="inlineStr"/>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AC207" s="5" t="inlineStr"/>
+      <c r="AD207" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="AE207" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AF207" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="AG207" s="5" t="inlineStr"/>
       <c r="AH207" s="5" t="inlineStr"/>
-      <c r="AI207" s="5" t="inlineStr"/>
+      <c r="AI207" s="5" t="n">
+        <v>59.11691541835818</v>
+      </c>
       <c r="AJ207" s="5" t="inlineStr"/>
-      <c r="AK207" s="5" t="inlineStr"/>
+      <c r="AK207" s="5" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AL207" s="5" t="inlineStr"/>
-      <c r="AM207" s="5" t="inlineStr"/>
-      <c r="AN207" s="5" t="inlineStr"/>
-      <c r="AO207" s="5" t="inlineStr"/>
-      <c r="AP207" s="5" t="inlineStr"/>
-      <c r="AQ207" s="5" t="inlineStr"/>
-      <c r="AR207" s="5" t="inlineStr"/>
-      <c r="AS207" s="5" t="inlineStr"/>
-      <c r="AT207" s="5" t="inlineStr"/>
-      <c r="AU207" s="5" t="inlineStr"/>
-      <c r="AV207" s="5" t="inlineStr"/>
-      <c r="AW207" s="5" t="inlineStr"/>
+      <c r="AM207" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN207" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO207" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP207" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ207" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AR207" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AS207" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AT207" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AU207" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AV207" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AW207" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="AX207" s="5" t="inlineStr"/>
       <c r="AY207" s="5" t="inlineStr"/>
       <c r="AZ207" s="5" t="inlineStr"/>
@@ -43418,12 +43490,12 @@
       <c r="B208" s="3" t="inlineStr"/>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Tim Hardaway</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -43443,12 +43515,12 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
@@ -43456,9 +43528,9 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="K208" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -43467,7 +43539,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="3" t="n">
-        <v>0.8423</v>
+        <v>0.8335</v>
       </c>
       <c r="P208" s="3" t="inlineStr"/>
       <c r="Q208" s="3" t="inlineStr"/>
@@ -43587,7 +43659,7 @@
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>Rebounds</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="I209" s="5" t="inlineStr">
@@ -43611,7 +43683,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="5" t="n">
-        <v>0.8525</v>
+        <v>0.8423</v>
       </c>
       <c r="P209" s="5" t="inlineStr"/>
       <c r="Q209" s="5" t="inlineStr"/>
@@ -43706,12 +43778,12 @@
       <c r="B210" s="3" t="inlineStr"/>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
@@ -43731,7 +43803,7 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Rebounds</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -43741,7 +43813,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -43755,7 +43827,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="3" t="n">
-        <v>0.8956</v>
+        <v>0.8525</v>
       </c>
       <c r="P210" s="3" t="inlineStr"/>
       <c r="Q210" s="3" t="inlineStr"/>
@@ -43875,17 +43947,17 @@
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="J211" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -43899,7 +43971,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>0.72</v>
+        <v>0.8956</v>
       </c>
       <c r="P211" s="5" t="inlineStr"/>
       <c r="Q211" s="5" t="inlineStr"/>
@@ -43980,6 +44052,150 @@
         </is>
       </c>
       <c r="BJ211" s="5" t="inlineStr">
+        <is>
+          <t>No spread data: 0.97x default</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr"/>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>G-F</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr"/>
+      <c r="M212" s="3" t="inlineStr"/>
+      <c r="N212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P212" s="3" t="inlineStr"/>
+      <c r="Q212" s="3" t="inlineStr"/>
+      <c r="R212" s="3" t="inlineStr"/>
+      <c r="S212" s="3" t="inlineStr"/>
+      <c r="T212" s="3" t="inlineStr"/>
+      <c r="U212" s="3" t="inlineStr"/>
+      <c r="V212" s="3" t="inlineStr"/>
+      <c r="W212" s="3" t="inlineStr"/>
+      <c r="X212" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y212" s="3" t="inlineStr">
+        <is>
+          <t>Above Avg</t>
+        </is>
+      </c>
+      <c r="Z212" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AA212" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB212" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AC212" s="3" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AD212" s="3" t="inlineStr"/>
+      <c r="AE212" s="3" t="inlineStr"/>
+      <c r="AF212" s="3" t="inlineStr"/>
+      <c r="AG212" s="3" t="inlineStr"/>
+      <c r="AH212" s="3" t="inlineStr"/>
+      <c r="AI212" s="3" t="inlineStr"/>
+      <c r="AJ212" s="3" t="inlineStr"/>
+      <c r="AK212" s="3" t="inlineStr"/>
+      <c r="AL212" s="3" t="inlineStr"/>
+      <c r="AM212" s="3" t="inlineStr"/>
+      <c r="AN212" s="3" t="inlineStr"/>
+      <c r="AO212" s="3" t="inlineStr"/>
+      <c r="AP212" s="3" t="inlineStr"/>
+      <c r="AQ212" s="3" t="inlineStr"/>
+      <c r="AR212" s="3" t="inlineStr"/>
+      <c r="AS212" s="3" t="inlineStr"/>
+      <c r="AT212" s="3" t="inlineStr"/>
+      <c r="AU212" s="3" t="inlineStr"/>
+      <c r="AV212" s="3" t="inlineStr"/>
+      <c r="AW212" s="3" t="inlineStr"/>
+      <c r="AX212" s="3" t="inlineStr"/>
+      <c r="AY212" s="3" t="inlineStr"/>
+      <c r="AZ212" s="3" t="inlineStr"/>
+      <c r="BA212" s="3" t="inlineStr"/>
+      <c r="BB212" s="3" t="inlineStr"/>
+      <c r="BC212" s="3" t="inlineStr"/>
+      <c r="BD212" s="3" t="inlineStr"/>
+      <c r="BE212" s="3" t="inlineStr"/>
+      <c r="BF212" s="3" t="inlineStr"/>
+      <c r="BG212" s="3" t="inlineStr"/>
+      <c r="BH212" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI212" s="3" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BJ212" s="3" t="inlineStr">
         <is>
           <t>No spread data: 0.97x default</t>
         </is>
@@ -70558,7 +70774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ93"/>
+  <dimension ref="A1:BJ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -82166,7 +82382,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
@@ -87938,24 +88154,24 @@
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
           <t>2026-04-30 21:30:00-04:00</t>
@@ -87981,30 +88197,46 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr"/>
-      <c r="M89" s="5" t="inlineStr"/>
+      <c r="L89" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N89" s="5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.8335</v>
+        <v>0.8636</v>
       </c>
       <c r="P89" s="5" t="inlineStr"/>
       <c r="Q89" s="5" t="inlineStr"/>
-      <c r="R89" s="5" t="inlineStr"/>
-      <c r="S89" s="5" t="inlineStr"/>
-      <c r="T89" s="5" t="inlineStr"/>
-      <c r="U89" s="5" t="inlineStr"/>
-      <c r="V89" s="5" t="inlineStr"/>
-      <c r="W89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S89" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T89" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W89" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="X89" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y89" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z89" s="5" t="inlineStr">
@@ -88019,34 +88251,90 @@
       </c>
       <c r="AB89" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AC89" s="5" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AD89" s="5" t="inlineStr"/>
-      <c r="AE89" s="5" t="inlineStr"/>
-      <c r="AF89" s="5" t="inlineStr"/>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AC89" s="5" t="inlineStr"/>
+      <c r="AD89" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="AE89" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AF89" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="AG89" s="5" t="inlineStr"/>
       <c r="AH89" s="5" t="inlineStr"/>
-      <c r="AI89" s="5" t="inlineStr"/>
+      <c r="AI89" s="5" t="n">
+        <v>59.11691541835818</v>
+      </c>
       <c r="AJ89" s="5" t="inlineStr"/>
-      <c r="AK89" s="5" t="inlineStr"/>
+      <c r="AK89" s="5" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="AL89" s="5" t="inlineStr"/>
-      <c r="AM89" s="5" t="inlineStr"/>
-      <c r="AN89" s="5" t="inlineStr"/>
-      <c r="AO89" s="5" t="inlineStr"/>
-      <c r="AP89" s="5" t="inlineStr"/>
-      <c r="AQ89" s="5" t="inlineStr"/>
-      <c r="AR89" s="5" t="inlineStr"/>
-      <c r="AS89" s="5" t="inlineStr"/>
-      <c r="AT89" s="5" t="inlineStr"/>
-      <c r="AU89" s="5" t="inlineStr"/>
-      <c r="AV89" s="5" t="inlineStr"/>
-      <c r="AW89" s="5" t="inlineStr"/>
+      <c r="AM89" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN89" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO89" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP89" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ89" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AR89" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AS89" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AT89" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AU89" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AV89" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AW89" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="AX89" s="5" t="inlineStr"/>
       <c r="AY89" s="5" t="inlineStr"/>
       <c r="AZ89" s="5" t="inlineStr"/>
@@ -88082,12 +88370,12 @@
       <c r="B90" s="3" t="inlineStr"/>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Tim Hardaway</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -88107,12 +88395,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -88120,9 +88408,9 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -88131,7 +88419,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0.8423</v>
+        <v>0.8335</v>
       </c>
       <c r="P90" s="3" t="inlineStr"/>
       <c r="Q90" s="3" t="inlineStr"/>
@@ -88251,7 +88539,7 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>Rebounds</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
@@ -88275,7 +88563,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0.8525</v>
+        <v>0.8423</v>
       </c>
       <c r="P91" s="5" t="inlineStr"/>
       <c r="Q91" s="5" t="inlineStr"/>
@@ -88370,12 +88658,12 @@
       <c r="B92" s="3" t="inlineStr"/>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -88395,7 +88683,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Rebounds</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -88405,7 +88693,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -88419,7 +88707,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.8956</v>
+        <v>0.8525</v>
       </c>
       <c r="P92" s="3" t="inlineStr"/>
       <c r="Q92" s="3" t="inlineStr"/>
@@ -88539,17 +88827,17 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -88563,7 +88851,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.72</v>
+        <v>0.8956</v>
       </c>
       <c r="P93" s="5" t="inlineStr"/>
       <c r="Q93" s="5" t="inlineStr"/>
@@ -88649,6 +88937,150 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr"/>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>G-F</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-30 21:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P94" s="3" t="inlineStr"/>
+      <c r="Q94" s="3" t="inlineStr"/>
+      <c r="R94" s="3" t="inlineStr"/>
+      <c r="S94" s="3" t="inlineStr"/>
+      <c r="T94" s="3" t="inlineStr"/>
+      <c r="U94" s="3" t="inlineStr"/>
+      <c r="V94" s="3" t="inlineStr"/>
+      <c r="W94" s="3" t="inlineStr"/>
+      <c r="X94" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y94" s="3" t="inlineStr">
+        <is>
+          <t>Above Avg</t>
+        </is>
+      </c>
+      <c r="Z94" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AA94" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB94" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AC94" s="3" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AD94" s="3" t="inlineStr"/>
+      <c r="AE94" s="3" t="inlineStr"/>
+      <c r="AF94" s="3" t="inlineStr"/>
+      <c r="AG94" s="3" t="inlineStr"/>
+      <c r="AH94" s="3" t="inlineStr"/>
+      <c r="AI94" s="3" t="inlineStr"/>
+      <c r="AJ94" s="3" t="inlineStr"/>
+      <c r="AK94" s="3" t="inlineStr"/>
+      <c r="AL94" s="3" t="inlineStr"/>
+      <c r="AM94" s="3" t="inlineStr"/>
+      <c r="AN94" s="3" t="inlineStr"/>
+      <c r="AO94" s="3" t="inlineStr"/>
+      <c r="AP94" s="3" t="inlineStr"/>
+      <c r="AQ94" s="3" t="inlineStr"/>
+      <c r="AR94" s="3" t="inlineStr"/>
+      <c r="AS94" s="3" t="inlineStr"/>
+      <c r="AT94" s="3" t="inlineStr"/>
+      <c r="AU94" s="3" t="inlineStr"/>
+      <c r="AV94" s="3" t="inlineStr"/>
+      <c r="AW94" s="3" t="inlineStr"/>
+      <c r="AX94" s="3" t="inlineStr"/>
+      <c r="AY94" s="3" t="inlineStr"/>
+      <c r="AZ94" s="3" t="inlineStr"/>
+      <c r="BA94" s="3" t="inlineStr"/>
+      <c r="BB94" s="3" t="inlineStr"/>
+      <c r="BC94" s="3" t="inlineStr"/>
+      <c r="BD94" s="3" t="inlineStr"/>
+      <c r="BE94" s="3" t="inlineStr"/>
+      <c r="BF94" s="3" t="inlineStr"/>
+      <c r="BG94" s="3" t="inlineStr"/>
+      <c r="BH94" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI94" s="3" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BJ94" s="3" t="inlineStr">
+        <is>
+          <t>No spread data: 0.97x default</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
